--- a/project_risk_template_v2_2_pt_BR.xlsx
+++ b/project_risk_template_v2_2_pt_BR.xlsx
@@ -29,7 +29,7 @@
   <definedNames>
     <definedName name="RiskCategoryOptions">Categorias_dos_Riscos!$A$3:$A$20</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
   <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -2348,7 +2348,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="155">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2767,6 +2767,33 @@
       <alignment vertical="center" wrapText="1" horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" horizontal="left"/>
     </xf>
   </cellXfs>
@@ -4495,17 +4522,17 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ActivitiesTable" displayName="ActivitiesTable" ref="A2:K99" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Activity_ID" dataDxfId="46"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Activity_Name" dataDxfId="45"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Predecessors" dataDxfId="44"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Duration_Model" dataDxfId="43"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Duration_Fixed" dataDxfId="42"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Duration_Min" dataDxfId="41"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Duration_MostLikely" dataDxfId="40"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Duration_Max" dataDxfId="39"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Duration_Mean" dataDxfId="38"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Duration_SD" dataDxfId="37"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Base_Cost" dataDxfId="36"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID_da_Atividade" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Nome_da_Atividade" dataDxfId="45"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Predecessoras" dataDxfId="44"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Modelo_de_Duracao" dataDxfId="43"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Duracao_Fixa" dataDxfId="42"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Duracao_Minima" dataDxfId="41"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Duracao_Mais_Provavel" dataDxfId="40"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Duracao_Maxima" dataDxfId="39"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Duracao_Media" dataDxfId="38"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Desvio_Padrao_da_Duracao" dataDxfId="37"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Custo_Fixo" dataDxfId="36"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4514,22 +4541,22 @@
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="RiskRegisterTable" displayName="RiskRegisterTable" ref="A2:P99" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65">
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Risk_ID" dataDxfId="64"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Risk_Name" dataDxfId="63"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Risk_Statement" dataDxfId="62"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Category" dataDxfId="61"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Risk_Type" dataDxfId="60"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Probability" dataDxfId="59"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Scope" dataDxfId="58"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Impact_Type" dataDxfId="57"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Trigger_Cause" dataDxfId="56"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Owner" dataDxfId="55"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Response_Strategy" dataDxfId="54"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Response_Action" dataDxfId="53"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Status" dataDxfId="52"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Impact_Distribution_Default" dataDxfId="51"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Notes" dataDxfId="50"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Active" dataDxfId="49"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="ID_do_Risco" dataDxfId="64"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Nome_do_Risco" dataDxfId="63"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Enunciado_do_Risco" dataDxfId="62"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Categoria" dataDxfId="61"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Tipo_de_Risco" dataDxfId="60"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Probabilidade" dataDxfId="59"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Abrangencia" dataDxfId="58"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Tipo_de_Impacto" dataDxfId="57"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Gatilho_Causa" dataDxfId="56"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Responsavel" dataDxfId="55"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Estrategia_de_Resposta" dataDxfId="54"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Acao_de_Resposta" dataDxfId="53"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Situacao" dataDxfId="52"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Distribuicao_Padrao_do_Impacto" dataDxfId="51"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Observacoes" dataDxfId="50"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Ativo" dataDxfId="49"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4538,16 +4565,16 @@
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="RiskActivityMapTable" displayName="RiskActivityMapTable" ref="A2:J99" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Risk_ID" dataDxfId="33"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Activity_ID" dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Impact_Type" dataDxfId="31"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Distribution" dataDxfId="30"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Impact_Fixed" dataDxfId="29"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Impact_Min" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Impact_MostLikely" dataDxfId="27"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Impact_Max" dataDxfId="26"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Impact_Mean" dataDxfId="25"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Impact_SD" dataDxfId="24"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="ID_do_Risco" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="ID_da_Atividade" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Tipo_de_Impacto" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Distribuicao" dataDxfId="30"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Impacto_Fixo" dataDxfId="29"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Impacto_Minimo" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Impacto_Mais_Provavel" dataDxfId="27"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Impacto_Maximo" dataDxfId="26"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Impacto_Medio" dataDxfId="25"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Desvio_Padrao_do_Impacto" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4556,12 +4583,12 @@
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="RiskRelationshipsTable" displayName="RiskRelationshipsTable" ref="A2:F99" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Parent_Risk" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Child_Risk" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Relationship_Type" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Influence_Parameter" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Active" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Notes" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Risco_Origem" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Risco_Destino" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Tipo_de_Relacao" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Parametro_de_Influencia" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Ativo" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Observacoes" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4570,11 +4597,11 @@
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="ValidationSpecTable" displayName="ValidationSpecTable" ref="A2:E15" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Area" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Rule" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Severity" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Example Message" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="Action" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Área" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Regra" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Severidade" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Mensagem de exemplo" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="Ação" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4775,7 +4802,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" style="12" customWidth="1"/>
@@ -5274,6 +5301,78 @@
       <c r="B41" s="127" t="inlineStr">
         <is>
           <t>Após alterações, recalcule e salve no Excel antes do envio. O aplicativo lê os resultados salvos das fórmulas. Não substitua fórmulas de custos vinculados por valores digitados, salvo ao abandonar deliberadamente esse fluxo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="75" customHeight="1">
+      <c r="A42" s="153" t="inlineStr">
+        <is>
+          <t>Parâmetros das distribuições</t>
+        </is>
+      </c>
+      <c r="B42" s="154" t="inlineStr">
+        <is>
+          <t>As células de parâmetros obrigatórios são destacadas conforme a distribuição selecionada; células não utilizadas permanecem neutras e seus conteúdos são preservados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="75" customHeight="1">
+      <c r="A43" s="153" t="inlineStr">
+        <is>
+          <t>Exponencial</t>
+        </is>
+      </c>
+      <c r="B43" s="154" t="inlineStr">
+        <is>
+          <t>Informe Média aritmética &gt; 0. Desvio-padrão e campos de três pontos não são utilizados. A distribuição é não negativa e não tem máximo finito.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="75" customHeight="1">
+      <c r="A44" s="153" t="inlineStr">
+        <is>
+          <t>Lognormal e Gama</t>
+        </is>
+      </c>
+      <c r="B44" s="154" t="inlineStr">
+        <is>
+          <t>Informe Média aritmética &gt; 0 e Desvio-padrão &gt; 0 nas unidades originais. Parâmetros logarítmicos e forma/escala de Gama são calculados internamente. Não se impõe máximo finito.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="75" customHeight="1">
+      <c r="A45" s="153" t="inlineStr">
+        <is>
+          <t>Distribuições opcionais de custo</t>
+        </is>
+      </c>
+      <c r="B45" s="154" t="inlineStr">
+        <is>
+          <t>Deixe Modelo_de_Custo em branco para manter o fluxo de Custo_Fixo vinculado. Um modelo explícito utiliza seus parâmetros de custo destacados para a parcela independente da duração; a taxa temporal e os custos diretos dos riscos continuam aplicáveis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="75" customHeight="1">
+      <c r="A46" s="153" t="inlineStr">
+        <is>
+          <t>Escopo das distribuições</t>
+        </is>
+      </c>
+      <c r="B46" s="154" t="inlineStr">
+        <is>
+          <t>As opções descrevem durações de atividades, custos intrínsecos e magnitudes de impactos mapeados. Probabilidades de ocorrência mantêm o suporte original Fixa/Uniforme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="75" customHeight="1">
+      <c r="A47" s="153" t="inlineStr">
+        <is>
+          <t>Média de referência</t>
+        </is>
+      </c>
+      <c r="B47" s="154" t="inlineStr">
+        <is>
+          <t>O CPM de referência e as fórmulas vinculadas de taxa de custo usam a Média aritmética informada para Exponencial, Lognormal e Gama. Recalcule e salve após alterações antes do envio.</t>
         </is>
       </c>
     </row>
@@ -6662,7 +6761,7 @@
         <v>12000</v>
       </c>
       <c r="C3" s="49">
-        <f>IF(Atividades!D3="Fixa",Atividades!E3,IF(Atividades!D3="Triangular",(Atividades!F3+Atividades!G3+Atividades!H3)/3,IF(Atividades!D3="Beta-PERT",(Atividades!F3+4*Atividades!G3+Atividades!H3)/6,IF(Atividades!D3="Normal",Atividades!I3,IF(Atividades!D3="Uniforme",(Atividades!F3+Atividades!H3)/2,NA())))))</f>
+        <f>IF(Atividades!D3="Fixa",Atividades!E3,IF(Atividades!D3="Triangular",(Atividades!F3+Atividades!G3+Atividades!H3)/3,IF(Atividades!D3="Beta-PERT",(Atividades!F3+4*Atividades!G3+Atividades!H3)/6,IF(Atividades!D3="Normal",Atividades!I3,IF(Atividades!D3="Uniforme",(Atividades!F3+Atividades!H3)/2,IF(OR(Atividades!D3="Exponencial",Atividades!D3="Lognormal",Atividades!D3="Gama"),Atividades!I3,NA()))))))</f>
         <v>3</v>
       </c>
       <c r="D3" s="50">
@@ -6698,7 +6797,7 @@
         <v>8000</v>
       </c>
       <c r="C4" s="49">
-        <f>IF(Atividades!D4="Fixa",Atividades!E4,IF(Atividades!D4="Triangular",(Atividades!F4+Atividades!G4+Atividades!H4)/3,IF(Atividades!D4="Beta-PERT",(Atividades!F4+4*Atividades!G4+Atividades!H4)/6,IF(Atividades!D4="Normal",Atividades!I4,IF(Atividades!D4="Uniforme",(Atividades!F4+Atividades!H4)/2,NA())))))</f>
+        <f>IF(Atividades!D4="Fixa",Atividades!E4,IF(Atividades!D4="Triangular",(Atividades!F4+Atividades!G4+Atividades!H4)/3,IF(Atividades!D4="Beta-PERT",(Atividades!F4+4*Atividades!G4+Atividades!H4)/6,IF(Atividades!D4="Normal",Atividades!I4,IF(Atividades!D4="Uniforme",(Atividades!F4+Atividades!H4)/2,IF(OR(Atividades!D4="Exponencial",Atividades!D4="Lognormal",Atividades!D4="Gama"),Atividades!I4,NA()))))))</f>
         <v>3.3333333333333335</v>
       </c>
       <c r="D4" s="50">
@@ -6734,7 +6833,7 @@
         <v>25000</v>
       </c>
       <c r="C5" s="49">
-        <f>IF(Atividades!D5="Fixa",Atividades!E5,IF(Atividades!D5="Triangular",(Atividades!F5+Atividades!G5+Atividades!H5)/3,IF(Atividades!D5="Beta-PERT",(Atividades!F5+4*Atividades!G5+Atividades!H5)/6,IF(Atividades!D5="Normal",Atividades!I5,IF(Atividades!D5="Uniforme",(Atividades!F5+Atividades!H5)/2,NA())))))</f>
+        <f>IF(Atividades!D5="Fixa",Atividades!E5,IF(Atividades!D5="Triangular",(Atividades!F5+Atividades!G5+Atividades!H5)/3,IF(Atividades!D5="Beta-PERT",(Atividades!F5+4*Atividades!G5+Atividades!H5)/6,IF(Atividades!D5="Normal",Atividades!I5,IF(Atividades!D5="Uniforme",(Atividades!F5+Atividades!H5)/2,IF(OR(Atividades!D5="Exponencial",Atividades!D5="Lognormal",Atividades!D5="Gama"),Atividades!I5,NA()))))))</f>
         <v>6.166666666666667</v>
       </c>
       <c r="D5" s="50">
@@ -6770,7 +6869,7 @@
         <v>18000</v>
       </c>
       <c r="C6" s="49">
-        <f>IF(Atividades!D6="Fixa",Atividades!E6,IF(Atividades!D6="Triangular",(Atividades!F6+Atividades!G6+Atividades!H6)/3,IF(Atividades!D6="Beta-PERT",(Atividades!F6+4*Atividades!G6+Atividades!H6)/6,IF(Atividades!D6="Normal",Atividades!I6,IF(Atividades!D6="Uniforme",(Atividades!F6+Atividades!H6)/2,NA())))))</f>
+        <f>IF(Atividades!D6="Fixa",Atividades!E6,IF(Atividades!D6="Triangular",(Atividades!F6+Atividades!G6+Atividades!H6)/3,IF(Atividades!D6="Beta-PERT",(Atividades!F6+4*Atividades!G6+Atividades!H6)/6,IF(Atividades!D6="Normal",Atividades!I6,IF(Atividades!D6="Uniforme",(Atividades!F6+Atividades!H6)/2,IF(OR(Atividades!D6="Exponencial",Atividades!D6="Lognormal",Atividades!D6="Gama"),Atividades!I6,NA()))))))</f>
         <v>5</v>
       </c>
       <c r="D6" s="50">
@@ -6806,7 +6905,7 @@
         <v>65000</v>
       </c>
       <c r="C7" s="49">
-        <f>IF(Atividades!D7="Fixa",Atividades!E7,IF(Atividades!D7="Triangular",(Atividades!F7+Atividades!G7+Atividades!H7)/3,IF(Atividades!D7="Beta-PERT",(Atividades!F7+4*Atividades!G7+Atividades!H7)/6,IF(Atividades!D7="Normal",Atividades!I7,IF(Atividades!D7="Uniforme",(Atividades!F7+Atividades!H7)/2,NA())))))</f>
+        <f>IF(Atividades!D7="Fixa",Atividades!E7,IF(Atividades!D7="Triangular",(Atividades!F7+Atividades!G7+Atividades!H7)/3,IF(Atividades!D7="Beta-PERT",(Atividades!F7+4*Atividades!G7+Atividades!H7)/6,IF(Atividades!D7="Normal",Atividades!I7,IF(Atividades!D7="Uniforme",(Atividades!F7+Atividades!H7)/2,IF(OR(Atividades!D7="Exponencial",Atividades!D7="Lognormal",Atividades!D7="Gama"),Atividades!I7,NA()))))))</f>
         <v>10</v>
       </c>
       <c r="D7" s="50">
@@ -6842,7 +6941,7 @@
         <v>38000</v>
       </c>
       <c r="C8" s="49">
-        <f>IF(Atividades!D8="Fixa",Atividades!E8,IF(Atividades!D8="Triangular",(Atividades!F8+Atividades!G8+Atividades!H8)/3,IF(Atividades!D8="Beta-PERT",(Atividades!F8+4*Atividades!G8+Atividades!H8)/6,IF(Atividades!D8="Normal",Atividades!I8,IF(Atividades!D8="Uniforme",(Atividades!F8+Atividades!H8)/2,NA())))))</f>
+        <f>IF(Atividades!D8="Fixa",Atividades!E8,IF(Atividades!D8="Triangular",(Atividades!F8+Atividades!G8+Atividades!H8)/3,IF(Atividades!D8="Beta-PERT",(Atividades!F8+4*Atividades!G8+Atividades!H8)/6,IF(Atividades!D8="Normal",Atividades!I8,IF(Atividades!D8="Uniforme",(Atividades!F8+Atividades!H8)/2,IF(OR(Atividades!D8="Exponencial",Atividades!D8="Lognormal",Atividades!D8="Gama"),Atividades!I8,NA()))))))</f>
         <v>6.333333333333333</v>
       </c>
       <c r="D8" s="50">
@@ -6878,7 +6977,7 @@
         <v>85000</v>
       </c>
       <c r="C9" s="49">
-        <f>IF(Atividades!D9="Fixa",Atividades!E9,IF(Atividades!D9="Triangular",(Atividades!F9+Atividades!G9+Atividades!H9)/3,IF(Atividades!D9="Beta-PERT",(Atividades!F9+4*Atividades!G9+Atividades!H9)/6,IF(Atividades!D9="Normal",Atividades!I9,IF(Atividades!D9="Uniforme",(Atividades!F9+Atividades!H9)/2,NA())))))</f>
+        <f>IF(Atividades!D9="Fixa",Atividades!E9,IF(Atividades!D9="Triangular",(Atividades!F9+Atividades!G9+Atividades!H9)/3,IF(Atividades!D9="Beta-PERT",(Atividades!F9+4*Atividades!G9+Atividades!H9)/6,IF(Atividades!D9="Normal",Atividades!I9,IF(Atividades!D9="Uniforme",(Atividades!F9+Atividades!H9)/2,IF(OR(Atividades!D9="Exponencial",Atividades!D9="Lognormal",Atividades!D9="Gama"),Atividades!I9,NA()))))))</f>
         <v>12.166666666666666</v>
       </c>
       <c r="D9" s="50">
@@ -6914,7 +7013,7 @@
         <v>82000</v>
       </c>
       <c r="C10" s="49">
-        <f>IF(Atividades!D10="Fixa",Atividades!E10,IF(Atividades!D10="Triangular",(Atividades!F10+Atividades!G10+Atividades!H10)/3,IF(Atividades!D10="Beta-PERT",(Atividades!F10+4*Atividades!G10+Atividades!H10)/6,IF(Atividades!D10="Normal",Atividades!I10,IF(Atividades!D10="Uniforme",(Atividades!F10+Atividades!H10)/2,NA())))))</f>
+        <f>IF(Atividades!D10="Fixa",Atividades!E10,IF(Atividades!D10="Triangular",(Atividades!F10+Atividades!G10+Atividades!H10)/3,IF(Atividades!D10="Beta-PERT",(Atividades!F10+4*Atividades!G10+Atividades!H10)/6,IF(Atividades!D10="Normal",Atividades!I10,IF(Atividades!D10="Uniforme",(Atividades!F10+Atividades!H10)/2,IF(OR(Atividades!D10="Exponencial",Atividades!D10="Lognormal",Atividades!D10="Gama"),Atividades!I10,NA()))))))</f>
         <v>11</v>
       </c>
       <c r="D10" s="50">
@@ -6950,7 +7049,7 @@
         <v>42000</v>
       </c>
       <c r="C11" s="49">
-        <f>IF(Atividades!D11="Fixa",Atividades!E11,IF(Atividades!D11="Triangular",(Atividades!F11+Atividades!G11+Atividades!H11)/3,IF(Atividades!D11="Beta-PERT",(Atividades!F11+4*Atividades!G11+Atividades!H11)/6,IF(Atividades!D11="Normal",Atividades!I11,IF(Atividades!D11="Uniforme",(Atividades!F11+Atividades!H11)/2,NA())))))</f>
+        <f>IF(Atividades!D11="Fixa",Atividades!E11,IF(Atividades!D11="Triangular",(Atividades!F11+Atividades!G11+Atividades!H11)/3,IF(Atividades!D11="Beta-PERT",(Atividades!F11+4*Atividades!G11+Atividades!H11)/6,IF(Atividades!D11="Normal",Atividades!I11,IF(Atividades!D11="Uniforme",(Atividades!F11+Atividades!H11)/2,IF(OR(Atividades!D11="Exponencial",Atividades!D11="Lognormal",Atividades!D11="Gama"),Atividades!I11,NA()))))))</f>
         <v>7</v>
       </c>
       <c r="D11" s="50">
@@ -6986,7 +7085,7 @@
         <v>50000</v>
       </c>
       <c r="C12" s="49">
-        <f>IF(Atividades!D12="Fixa",Atividades!E12,IF(Atividades!D12="Triangular",(Atividades!F12+Atividades!G12+Atividades!H12)/3,IF(Atividades!D12="Beta-PERT",(Atividades!F12+4*Atividades!G12+Atividades!H12)/6,IF(Atividades!D12="Normal",Atividades!I12,IF(Atividades!D12="Uniforme",(Atividades!F12+Atividades!H12)/2,NA())))))</f>
+        <f>IF(Atividades!D12="Fixa",Atividades!E12,IF(Atividades!D12="Triangular",(Atividades!F12+Atividades!G12+Atividades!H12)/3,IF(Atividades!D12="Beta-PERT",(Atividades!F12+4*Atividades!G12+Atividades!H12)/6,IF(Atividades!D12="Normal",Atividades!I12,IF(Atividades!D12="Uniforme",(Atividades!F12+Atividades!H12)/2,IF(OR(Atividades!D12="Exponencial",Atividades!D12="Lognormal",Atividades!D12="Gama"),Atividades!I12,NA()))))))</f>
         <v>10.666666666666666</v>
       </c>
       <c r="D12" s="50">
@@ -7022,7 +7121,7 @@
         <v>32000</v>
       </c>
       <c r="C13" s="49">
-        <f>IF(Atividades!D13="Fixa",Atividades!E13,IF(Atividades!D13="Triangular",(Atividades!F13+Atividades!G13+Atividades!H13)/3,IF(Atividades!D13="Beta-PERT",(Atividades!F13+4*Atividades!G13+Atividades!H13)/6,IF(Atividades!D13="Normal",Atividades!I13,IF(Atividades!D13="Uniforme",(Atividades!F13+Atividades!H13)/2,NA())))))</f>
+        <f>IF(Atividades!D13="Fixa",Atividades!E13,IF(Atividades!D13="Triangular",(Atividades!F13+Atividades!G13+Atividades!H13)/3,IF(Atividades!D13="Beta-PERT",(Atividades!F13+4*Atividades!G13+Atividades!H13)/6,IF(Atividades!D13="Normal",Atividades!I13,IF(Atividades!D13="Uniforme",(Atividades!F13+Atividades!H13)/2,IF(OR(Atividades!D13="Exponencial",Atividades!D13="Lognormal",Atividades!D13="Gama"),Atividades!I13,NA()))))))</f>
         <v>8.3333333333333339</v>
       </c>
       <c r="D13" s="50">
@@ -7058,7 +7157,7 @@
         <v>35000</v>
       </c>
       <c r="C14" s="49">
-        <f>IF(Atividades!D14="Fixa",Atividades!E14,IF(Atividades!D14="Triangular",(Atividades!F14+Atividades!G14+Atividades!H14)/3,IF(Atividades!D14="Beta-PERT",(Atividades!F14+4*Atividades!G14+Atividades!H14)/6,IF(Atividades!D14="Normal",Atividades!I14,IF(Atividades!D14="Uniforme",(Atividades!F14+Atividades!H14)/2,NA())))))</f>
+        <f>IF(Atividades!D14="Fixa",Atividades!E14,IF(Atividades!D14="Triangular",(Atividades!F14+Atividades!G14+Atividades!H14)/3,IF(Atividades!D14="Beta-PERT",(Atividades!F14+4*Atividades!G14+Atividades!H14)/6,IF(Atividades!D14="Normal",Atividades!I14,IF(Atividades!D14="Uniforme",(Atividades!F14+Atividades!H14)/2,IF(OR(Atividades!D14="Exponencial",Atividades!D14="Lognormal",Atividades!D14="Gama"),Atividades!I14,NA()))))))</f>
         <v>8</v>
       </c>
       <c r="D14" s="50">
@@ -7094,7 +7193,7 @@
         <v>36000</v>
       </c>
       <c r="C15" s="49">
-        <f>IF(Atividades!D15="Fixa",Atividades!E15,IF(Atividades!D15="Triangular",(Atividades!F15+Atividades!G15+Atividades!H15)/3,IF(Atividades!D15="Beta-PERT",(Atividades!F15+4*Atividades!G15+Atividades!H15)/6,IF(Atividades!D15="Normal",Atividades!I15,IF(Atividades!D15="Uniforme",(Atividades!F15+Atividades!H15)/2,NA())))))</f>
+        <f>IF(Atividades!D15="Fixa",Atividades!E15,IF(Atividades!D15="Triangular",(Atividades!F15+Atividades!G15+Atividades!H15)/3,IF(Atividades!D15="Beta-PERT",(Atividades!F15+4*Atividades!G15+Atividades!H15)/6,IF(Atividades!D15="Normal",Atividades!I15,IF(Atividades!D15="Uniforme",(Atividades!F15+Atividades!H15)/2,IF(OR(Atividades!D15="Exponencial",Atividades!D15="Lognormal",Atividades!D15="Gama"),Atividades!I15,NA()))))))</f>
         <v>8</v>
       </c>
       <c r="D15" s="50">
@@ -7130,7 +7229,7 @@
         <v>28000</v>
       </c>
       <c r="C16" s="49">
-        <f>IF(Atividades!D16="Fixa",Atividades!E16,IF(Atividades!D16="Triangular",(Atividades!F16+Atividades!G16+Atividades!H16)/3,IF(Atividades!D16="Beta-PERT",(Atividades!F16+4*Atividades!G16+Atividades!H16)/6,IF(Atividades!D16="Normal",Atividades!I16,IF(Atividades!D16="Uniforme",(Atividades!F16+Atividades!H16)/2,NA())))))</f>
+        <f>IF(Atividades!D16="Fixa",Atividades!E16,IF(Atividades!D16="Triangular",(Atividades!F16+Atividades!G16+Atividades!H16)/3,IF(Atividades!D16="Beta-PERT",(Atividades!F16+4*Atividades!G16+Atividades!H16)/6,IF(Atividades!D16="Normal",Atividades!I16,IF(Atividades!D16="Uniforme",(Atividades!F16+Atividades!H16)/2,IF(OR(Atividades!D16="Exponencial",Atividades!D16="Lognormal",Atividades!D16="Gama"),Atividades!I16,NA()))))))</f>
         <v>6.666666666666667</v>
       </c>
       <c r="D16" s="50">
@@ -7166,7 +7265,7 @@
         <v>45000</v>
       </c>
       <c r="C17" s="49">
-        <f>IF(Atividades!D17="Fixa",Atividades!E17,IF(Atividades!D17="Triangular",(Atividades!F17+Atividades!G17+Atividades!H17)/3,IF(Atividades!D17="Beta-PERT",(Atividades!F17+4*Atividades!G17+Atividades!H17)/6,IF(Atividades!D17="Normal",Atividades!I17,IF(Atividades!D17="Uniforme",(Atividades!F17+Atividades!H17)/2,NA())))))</f>
+        <f>IF(Atividades!D17="Fixa",Atividades!E17,IF(Atividades!D17="Triangular",(Atividades!F17+Atividades!G17+Atividades!H17)/3,IF(Atividades!D17="Beta-PERT",(Atividades!F17+4*Atividades!G17+Atividades!H17)/6,IF(Atividades!D17="Normal",Atividades!I17,IF(Atividades!D17="Uniforme",(Atividades!F17+Atividades!H17)/2,IF(OR(Atividades!D17="Exponencial",Atividades!D17="Lognormal",Atividades!D17="Gama"),Atividades!I17,NA()))))))</f>
         <v>6.333333333333333</v>
       </c>
       <c r="D17" s="50">
@@ -7202,7 +7301,7 @@
         <v>22000</v>
       </c>
       <c r="C18" s="49">
-        <f>IF(Atividades!D18="Fixa",Atividades!E18,IF(Atividades!D18="Triangular",(Atividades!F18+Atividades!G18+Atividades!H18)/3,IF(Atividades!D18="Beta-PERT",(Atividades!F18+4*Atividades!G18+Atividades!H18)/6,IF(Atividades!D18="Normal",Atividades!I18,IF(Atividades!D18="Uniforme",(Atividades!F18+Atividades!H18)/2,NA())))))</f>
+        <f>IF(Atividades!D18="Fixa",Atividades!E18,IF(Atividades!D18="Triangular",(Atividades!F18+Atividades!G18+Atividades!H18)/3,IF(Atividades!D18="Beta-PERT",(Atividades!F18+4*Atividades!G18+Atividades!H18)/6,IF(Atividades!D18="Normal",Atividades!I18,IF(Atividades!D18="Uniforme",(Atividades!F18+Atividades!H18)/2,IF(OR(Atividades!D18="Exponencial",Atividades!D18="Lognormal",Atividades!D18="Gama"),Atividades!I18,NA()))))))</f>
         <v>5</v>
       </c>
       <c r="D18" s="50">
@@ -7238,7 +7337,7 @@
         <v>40000</v>
       </c>
       <c r="C19" s="49">
-        <f>IF(Atividades!D19="Fixa",Atividades!E19,IF(Atividades!D19="Triangular",(Atividades!F19+Atividades!G19+Atividades!H19)/3,IF(Atividades!D19="Beta-PERT",(Atividades!F19+4*Atividades!G19+Atividades!H19)/6,IF(Atividades!D19="Normal",Atividades!I19,IF(Atividades!D19="Uniforme",(Atividades!F19+Atividades!H19)/2,NA())))))</f>
+        <f>IF(Atividades!D19="Fixa",Atividades!E19,IF(Atividades!D19="Triangular",(Atividades!F19+Atividades!G19+Atividades!H19)/3,IF(Atividades!D19="Beta-PERT",(Atividades!F19+4*Atividades!G19+Atividades!H19)/6,IF(Atividades!D19="Normal",Atividades!I19,IF(Atividades!D19="Uniforme",(Atividades!F19+Atividades!H19)/2,IF(OR(Atividades!D19="Exponencial",Atividades!D19="Lognormal",Atividades!D19="Gama"),Atividades!I19,NA()))))))</f>
         <v>9</v>
       </c>
       <c r="D19" s="50">
@@ -7274,7 +7373,7 @@
         <v>48000</v>
       </c>
       <c r="C20" s="49">
-        <f>IF(Atividades!D20="Fixa",Atividades!E20,IF(Atividades!D20="Triangular",(Atividades!F20+Atividades!G20+Atividades!H20)/3,IF(Atividades!D20="Beta-PERT",(Atividades!F20+4*Atividades!G20+Atividades!H20)/6,IF(Atividades!D20="Normal",Atividades!I20,IF(Atividades!D20="Uniforme",(Atividades!F20+Atividades!H20)/2,NA())))))</f>
+        <f>IF(Atividades!D20="Fixa",Atividades!E20,IF(Atividades!D20="Triangular",(Atividades!F20+Atividades!G20+Atividades!H20)/3,IF(Atividades!D20="Beta-PERT",(Atividades!F20+4*Atividades!G20+Atividades!H20)/6,IF(Atividades!D20="Normal",Atividades!I20,IF(Atividades!D20="Uniforme",(Atividades!F20+Atividades!H20)/2,IF(OR(Atividades!D20="Exponencial",Atividades!D20="Lognormal",Atividades!D20="Gama"),Atividades!I20,NA()))))))</f>
         <v>9.6666666666666661</v>
       </c>
       <c r="D20" s="50">
@@ -7310,7 +7409,7 @@
         <v>52000</v>
       </c>
       <c r="C21" s="49">
-        <f>IF(Atividades!D21="Fixa",Atividades!E21,IF(Atividades!D21="Triangular",(Atividades!F21+Atividades!G21+Atividades!H21)/3,IF(Atividades!D21="Beta-PERT",(Atividades!F21+4*Atividades!G21+Atividades!H21)/6,IF(Atividades!D21="Normal",Atividades!I21,IF(Atividades!D21="Uniforme",(Atividades!F21+Atividades!H21)/2,NA())))))</f>
+        <f>IF(Atividades!D21="Fixa",Atividades!E21,IF(Atividades!D21="Triangular",(Atividades!F21+Atividades!G21+Atividades!H21)/3,IF(Atividades!D21="Beta-PERT",(Atividades!F21+4*Atividades!G21+Atividades!H21)/6,IF(Atividades!D21="Normal",Atividades!I21,IF(Atividades!D21="Uniforme",(Atividades!F21+Atividades!H21)/2,IF(OR(Atividades!D21="Exponencial",Atividades!D21="Lognormal",Atividades!D21="Gama"),Atividades!I21,NA()))))))</f>
         <v>9.1666666666666661</v>
       </c>
       <c r="D21" s="50">
@@ -7346,7 +7445,7 @@
         <v>26000</v>
       </c>
       <c r="C22" s="49">
-        <f>IF(Atividades!D22="Fixa",Atividades!E22,IF(Atividades!D22="Triangular",(Atividades!F22+Atividades!G22+Atividades!H22)/3,IF(Atividades!D22="Beta-PERT",(Atividades!F22+4*Atividades!G22+Atividades!H22)/6,IF(Atividades!D22="Normal",Atividades!I22,IF(Atividades!D22="Uniforme",(Atividades!F22+Atividades!H22)/2,NA())))))</f>
+        <f>IF(Atividades!D22="Fixa",Atividades!E22,IF(Atividades!D22="Triangular",(Atividades!F22+Atividades!G22+Atividades!H22)/3,IF(Atividades!D22="Beta-PERT",(Atividades!F22+4*Atividades!G22+Atividades!H22)/6,IF(Atividades!D22="Normal",Atividades!I22,IF(Atividades!D22="Uniforme",(Atividades!F22+Atividades!H22)/2,IF(OR(Atividades!D22="Exponencial",Atividades!D22="Lognormal",Atividades!D22="Gama"),Atividades!I22,NA()))))))</f>
         <v>6</v>
       </c>
       <c r="D22" s="50">
@@ -7382,7 +7481,7 @@
         <v>38000</v>
       </c>
       <c r="C23" s="49">
-        <f>IF(Atividades!D23="Fixa",Atividades!E23,IF(Atividades!D23="Triangular",(Atividades!F23+Atividades!G23+Atividades!H23)/3,IF(Atividades!D23="Beta-PERT",(Atividades!F23+4*Atividades!G23+Atividades!H23)/6,IF(Atividades!D23="Normal",Atividades!I23,IF(Atividades!D23="Uniforme",(Atividades!F23+Atividades!H23)/2,NA())))))</f>
+        <f>IF(Atividades!D23="Fixa",Atividades!E23,IF(Atividades!D23="Triangular",(Atividades!F23+Atividades!G23+Atividades!H23)/3,IF(Atividades!D23="Beta-PERT",(Atividades!F23+4*Atividades!G23+Atividades!H23)/6,IF(Atividades!D23="Normal",Atividades!I23,IF(Atividades!D23="Uniforme",(Atividades!F23+Atividades!H23)/2,IF(OR(Atividades!D23="Exponencial",Atividades!D23="Lognormal",Atividades!D23="Gama"),Atividades!I23,NA()))))))</f>
         <v>9</v>
       </c>
       <c r="D23" s="50">
@@ -7418,7 +7517,7 @@
         <v>30000</v>
       </c>
       <c r="C24" s="49">
-        <f>IF(Atividades!D24="Fixa",Atividades!E24,IF(Atividades!D24="Triangular",(Atividades!F24+Atividades!G24+Atividades!H24)/3,IF(Atividades!D24="Beta-PERT",(Atividades!F24+4*Atividades!G24+Atividades!H24)/6,IF(Atividades!D24="Normal",Atividades!I24,IF(Atividades!D24="Uniforme",(Atividades!F24+Atividades!H24)/2,NA())))))</f>
+        <f>IF(Atividades!D24="Fixa",Atividades!E24,IF(Atividades!D24="Triangular",(Atividades!F24+Atividades!G24+Atividades!H24)/3,IF(Atividades!D24="Beta-PERT",(Atividades!F24+4*Atividades!G24+Atividades!H24)/6,IF(Atividades!D24="Normal",Atividades!I24,IF(Atividades!D24="Uniforme",(Atividades!F24+Atividades!H24)/2,IF(OR(Atividades!D24="Exponencial",Atividades!D24="Lognormal",Atividades!D24="Gama"),Atividades!I24,NA()))))))</f>
         <v>6.333333333333333</v>
       </c>
       <c r="D24" s="50">
@@ -7454,7 +7553,7 @@
         <v>32000</v>
       </c>
       <c r="C25" s="49">
-        <f>IF(Atividades!D25="Fixa",Atividades!E25,IF(Atividades!D25="Triangular",(Atividades!F25+Atividades!G25+Atividades!H25)/3,IF(Atividades!D25="Beta-PERT",(Atividades!F25+4*Atividades!G25+Atividades!H25)/6,IF(Atividades!D25="Normal",Atividades!I25,IF(Atividades!D25="Uniforme",(Atividades!F25+Atividades!H25)/2,NA())))))</f>
+        <f>IF(Atividades!D25="Fixa",Atividades!E25,IF(Atividades!D25="Triangular",(Atividades!F25+Atividades!G25+Atividades!H25)/3,IF(Atividades!D25="Beta-PERT",(Atividades!F25+4*Atividades!G25+Atividades!H25)/6,IF(Atividades!D25="Normal",Atividades!I25,IF(Atividades!D25="Uniforme",(Atividades!F25+Atividades!H25)/2,IF(OR(Atividades!D25="Exponencial",Atividades!D25="Lognormal",Atividades!D25="Gama"),Atividades!I25,NA()))))))</f>
         <v>6.166666666666667</v>
       </c>
       <c r="D25" s="50">
@@ -7490,7 +7589,7 @@
         <v>42000</v>
       </c>
       <c r="C26" s="49">
-        <f>IF(Atividades!D26="Fixa",Atividades!E26,IF(Atividades!D26="Triangular",(Atividades!F26+Atividades!G26+Atividades!H26)/3,IF(Atividades!D26="Beta-PERT",(Atividades!F26+4*Atividades!G26+Atividades!H26)/6,IF(Atividades!D26="Normal",Atividades!I26,IF(Atividades!D26="Uniforme",(Atividades!F26+Atividades!H26)/2,NA())))))</f>
+        <f>IF(Atividades!D26="Fixa",Atividades!E26,IF(Atividades!D26="Triangular",(Atividades!F26+Atividades!G26+Atividades!H26)/3,IF(Atividades!D26="Beta-PERT",(Atividades!F26+4*Atividades!G26+Atividades!H26)/6,IF(Atividades!D26="Normal",Atividades!I26,IF(Atividades!D26="Uniforme",(Atividades!F26+Atividades!H26)/2,IF(OR(Atividades!D26="Exponencial",Atividades!D26="Lognormal",Atividades!D26="Gama"),Atividades!I26,NA()))))))</f>
         <v>8</v>
       </c>
       <c r="D26" s="50">
@@ -7526,7 +7625,7 @@
         <v>55000</v>
       </c>
       <c r="C27" s="49">
-        <f>IF(Atividades!D27="Fixa",Atividades!E27,IF(Atividades!D27="Triangular",(Atividades!F27+Atividades!G27+Atividades!H27)/3,IF(Atividades!D27="Beta-PERT",(Atividades!F27+4*Atividades!G27+Atividades!H27)/6,IF(Atividades!D27="Normal",Atividades!I27,IF(Atividades!D27="Uniforme",(Atividades!F27+Atividades!H27)/2,NA())))))</f>
+        <f>IF(Atividades!D27="Fixa",Atividades!E27,IF(Atividades!D27="Triangular",(Atividades!F27+Atividades!G27+Atividades!H27)/3,IF(Atividades!D27="Beta-PERT",(Atividades!F27+4*Atividades!G27+Atividades!H27)/6,IF(Atividades!D27="Normal",Atividades!I27,IF(Atividades!D27="Uniforme",(Atividades!F27+Atividades!H27)/2,IF(OR(Atividades!D27="Exponencial",Atividades!D27="Lognormal",Atividades!D27="Gama"),Atividades!I27,NA()))))))</f>
         <v>9</v>
       </c>
       <c r="D27" s="50">
@@ -7562,7 +7661,7 @@
         <v>18000</v>
       </c>
       <c r="C28" s="49">
-        <f>IF(Atividades!D28="Fixa",Atividades!E28,IF(Atividades!D28="Triangular",(Atividades!F28+Atividades!G28+Atividades!H28)/3,IF(Atividades!D28="Beta-PERT",(Atividades!F28+4*Atividades!G28+Atividades!H28)/6,IF(Atividades!D28="Normal",Atividades!I28,IF(Atividades!D28="Uniforme",(Atividades!F28+Atividades!H28)/2,NA())))))</f>
+        <f>IF(Atividades!D28="Fixa",Atividades!E28,IF(Atividades!D28="Triangular",(Atividades!F28+Atividades!G28+Atividades!H28)/3,IF(Atividades!D28="Beta-PERT",(Atividades!F28+4*Atividades!G28+Atividades!H28)/6,IF(Atividades!D28="Normal",Atividades!I28,IF(Atividades!D28="Uniforme",(Atividades!F28+Atividades!H28)/2,IF(OR(Atividades!D28="Exponencial",Atividades!D28="Lognormal",Atividades!D28="Gama"),Atividades!I28,NA()))))))</f>
         <v>5.333333333333333</v>
       </c>
       <c r="D28" s="50">
@@ -7598,7 +7697,7 @@
         <v>20000</v>
       </c>
       <c r="C29" s="49">
-        <f>IF(Atividades!D29="Fixa",Atividades!E29,IF(Atividades!D29="Triangular",(Atividades!F29+Atividades!G29+Atividades!H29)/3,IF(Atividades!D29="Beta-PERT",(Atividades!F29+4*Atividades!G29+Atividades!H29)/6,IF(Atividades!D29="Normal",Atividades!I29,IF(Atividades!D29="Uniforme",(Atividades!F29+Atividades!H29)/2,NA())))))</f>
+        <f>IF(Atividades!D29="Fixa",Atividades!E29,IF(Atividades!D29="Triangular",(Atividades!F29+Atividades!G29+Atividades!H29)/3,IF(Atividades!D29="Beta-PERT",(Atividades!F29+4*Atividades!G29+Atividades!H29)/6,IF(Atividades!D29="Normal",Atividades!I29,IF(Atividades!D29="Uniforme",(Atividades!F29+Atividades!H29)/2,IF(OR(Atividades!D29="Exponencial",Atividades!D29="Lognormal",Atividades!D29="Gama"),Atividades!I29,NA()))))))</f>
         <v>6.333333333333333</v>
       </c>
       <c r="D29" s="50">
@@ -7634,7 +7733,7 @@
         <v>15000</v>
       </c>
       <c r="C30" s="49">
-        <f>IF(Atividades!D30="Fixa",Atividades!E30,IF(Atividades!D30="Triangular",(Atividades!F30+Atividades!G30+Atividades!H30)/3,IF(Atividades!D30="Beta-PERT",(Atividades!F30+4*Atividades!G30+Atividades!H30)/6,IF(Atividades!D30="Normal",Atividades!I30,IF(Atividades!D30="Uniforme",(Atividades!F30+Atividades!H30)/2,NA())))))</f>
+        <f>IF(Atividades!D30="Fixa",Atividades!E30,IF(Atividades!D30="Triangular",(Atividades!F30+Atividades!G30+Atividades!H30)/3,IF(Atividades!D30="Beta-PERT",(Atividades!F30+4*Atividades!G30+Atividades!H30)/6,IF(Atividades!D30="Normal",Atividades!I30,IF(Atividades!D30="Uniforme",(Atividades!F30+Atividades!H30)/2,IF(OR(Atividades!D30="Exponencial",Atividades!D30="Lognormal",Atividades!D30="Gama"),Atividades!I30,NA()))))))</f>
         <v>5</v>
       </c>
       <c r="D30" s="50">
@@ -7670,7 +7769,7 @@
         <v>10000</v>
       </c>
       <c r="C31" s="49">
-        <f>IF(Atividades!D31="Fixa",Atividades!E31,IF(Atividades!D31="Triangular",(Atividades!F31+Atividades!G31+Atividades!H31)/3,IF(Atividades!D31="Beta-PERT",(Atividades!F31+4*Atividades!G31+Atividades!H31)/6,IF(Atividades!D31="Normal",Atividades!I31,IF(Atividades!D31="Uniforme",(Atividades!F31+Atividades!H31)/2,NA())))))</f>
+        <f>IF(Atividades!D31="Fixa",Atividades!E31,IF(Atividades!D31="Triangular",(Atividades!F31+Atividades!G31+Atividades!H31)/3,IF(Atividades!D31="Beta-PERT",(Atividades!F31+4*Atividades!G31+Atividades!H31)/6,IF(Atividades!D31="Normal",Atividades!I31,IF(Atividades!D31="Uniforme",(Atividades!F31+Atividades!H31)/2,IF(OR(Atividades!D31="Exponencial",Atividades!D31="Lognormal",Atividades!D31="Gama"),Atividades!I31,NA()))))))</f>
         <v>4.333333333333333</v>
       </c>
       <c r="D31" s="50">
@@ -7706,7 +7805,7 @@
         <v>8000</v>
       </c>
       <c r="C32" s="49">
-        <f>IF(Atividades!D32="Fixa",Atividades!E32,IF(Atividades!D32="Triangular",(Atividades!F32+Atividades!G32+Atividades!H32)/3,IF(Atividades!D32="Beta-PERT",(Atividades!F32+4*Atividades!G32+Atividades!H32)/6,IF(Atividades!D32="Normal",Atividades!I32,IF(Atividades!D32="Uniforme",(Atividades!F32+Atividades!H32)/2,NA())))))</f>
+        <f>IF(Atividades!D32="Fixa",Atividades!E32,IF(Atividades!D32="Triangular",(Atividades!F32+Atividades!G32+Atividades!H32)/3,IF(Atividades!D32="Beta-PERT",(Atividades!F32+4*Atividades!G32+Atividades!H32)/6,IF(Atividades!D32="Normal",Atividades!I32,IF(Atividades!D32="Uniforme",(Atividades!F32+Atividades!H32)/2,IF(OR(Atividades!D32="Exponencial",Atividades!D32="Lognormal",Atividades!D32="Gama"),Atividades!I32,NA()))))))</f>
         <v>2.1666666666666665</v>
       </c>
       <c r="D32" s="50">
@@ -8142,7 +8241,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:M99"/>
+  <dimension ref="A1:T99"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.625" style="9" customWidth="1"/>
@@ -8154,7 +8253,14 @@
     <col min="8" max="11" width="14" style="9" customWidth="1"/>
     <col min="12" max="12" width="13" style="9" customWidth="1"/>
     <col min="13" max="13" width="15.75" style="9" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="2"/>
+    <col min="14" max="14" width="24" customWidth="1"/>
+    <col min="15" max="15" width="24" customWidth="1"/>
+    <col min="16" max="16" width="24" customWidth="1"/>
+    <col min="17" max="17" width="24" customWidth="1"/>
+    <col min="18" max="18" width="24" customWidth="1"/>
+    <col min="19" max="19" width="24" customWidth="1"/>
+    <col min="20" max="20" width="24" customWidth="1"/>
+    <col min="21" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" ht="26.25" customHeight="1">
@@ -8176,7 +8282,7 @@
       <c r="L1" s="25"/>
       <c r="M1" s="25"/>
     </row>
-    <row r="2" spans="1:13" ht="51" customHeight="1">
+    <row r="2" spans="1:13" ht="65" customHeight="1">
       <c r="A2" s="78" t="inlineStr">
         <is>
           <t>ID_da_Atividade</t>
@@ -8240,6 +8346,41 @@
       <c r="M2" s="78" t="inlineStr">
         <is>
           <t>Associacao_de_Custo</t>
+        </is>
+      </c>
+      <c r="N2" s="146" t="inlineStr">
+        <is>
+          <t>Modelo_de_Custo</t>
+        </is>
+      </c>
+      <c r="O2" s="147" t="inlineStr">
+        <is>
+          <t>Valor_Fixo_do_Modelo_de_Custo</t>
+        </is>
+      </c>
+      <c r="P2" s="148" t="inlineStr">
+        <is>
+          <t>Custo_Minimo</t>
+        </is>
+      </c>
+      <c r="Q2" s="149" t="inlineStr">
+        <is>
+          <t>Custo_Mais_Provavel</t>
+        </is>
+      </c>
+      <c r="R2" s="150" t="inlineStr">
+        <is>
+          <t>Custo_Maximo</t>
+        </is>
+      </c>
+      <c r="S2" s="151" t="inlineStr">
+        <is>
+          <t>Custo_Medio</t>
+        </is>
+      </c>
+      <c r="T2" s="152" t="inlineStr">
+        <is>
+          <t>Desvio_Padrao_do_Custo</t>
         </is>
       </c>
     </row>
@@ -8279,6 +8420,13 @@
           <t>Fixo + tempo</t>
         </is>
       </c>
+      <c r="N3" s="131"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="21"/>
+      <c r="Q3" s="21"/>
+      <c r="R3" s="21"/>
+      <c r="S3" s="21"/>
+      <c r="T3" s="21"/>
     </row>
     <row r="4" spans="1:13" ht="36" customHeight="1">
       <c r="A4" s="19" t="s">
@@ -8320,6 +8468,13 @@
           <t>Fixo + tempo</t>
         </is>
       </c>
+      <c r="N4" s="6"/>
+      <c r="O4" s="21"/>
+      <c r="P4" s="21"/>
+      <c r="Q4" s="21"/>
+      <c r="R4" s="21"/>
+      <c r="S4" s="21"/>
+      <c r="T4" s="21"/>
     </row>
     <row r="5" spans="1:13" ht="36" customHeight="1">
       <c r="A5" s="19" t="s">
@@ -8361,6 +8516,13 @@
           <t>Fixo + tempo</t>
         </is>
       </c>
+      <c r="N5" s="6"/>
+      <c r="O5" s="21"/>
+      <c r="P5" s="21"/>
+      <c r="Q5" s="21"/>
+      <c r="R5" s="21"/>
+      <c r="S5" s="21"/>
+      <c r="T5" s="21"/>
     </row>
     <row r="6" spans="1:13" ht="21" customHeight="1">
       <c r="A6" s="19" t="s">
@@ -8400,6 +8562,13 @@
           <t>Fixo + tempo</t>
         </is>
       </c>
+      <c r="N6" s="6"/>
+      <c r="O6" s="21"/>
+      <c r="P6" s="21"/>
+      <c r="Q6" s="21"/>
+      <c r="R6" s="21"/>
+      <c r="S6" s="21"/>
+      <c r="T6" s="21"/>
     </row>
     <row r="7" spans="1:13" ht="21" customHeight="1">
       <c r="A7" s="19" t="s">
@@ -8439,6 +8608,13 @@
           <t>Fixo + tempo</t>
         </is>
       </c>
+      <c r="N7" s="131"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="21"/>
+      <c r="Q7" s="21"/>
+      <c r="R7" s="21"/>
+      <c r="S7" s="21"/>
+      <c r="T7" s="21"/>
     </row>
     <row r="8" spans="1:13" ht="21" customHeight="1">
       <c r="A8" s="19" t="s">
@@ -8480,6 +8656,13 @@
           <t>Fixo + tempo</t>
         </is>
       </c>
+      <c r="N8" s="6"/>
+      <c r="O8" s="21"/>
+      <c r="P8" s="21"/>
+      <c r="Q8" s="21"/>
+      <c r="R8" s="21"/>
+      <c r="S8" s="21"/>
+      <c r="T8" s="21"/>
     </row>
     <row r="9" spans="1:13" ht="36" customHeight="1">
       <c r="A9" s="19" t="s">
@@ -8521,6 +8704,13 @@
           <t>Fixo + tempo</t>
         </is>
       </c>
+      <c r="N9" s="6"/>
+      <c r="O9" s="21"/>
+      <c r="P9" s="21"/>
+      <c r="Q9" s="21"/>
+      <c r="R9" s="21"/>
+      <c r="S9" s="21"/>
+      <c r="T9" s="21"/>
     </row>
     <row r="10" spans="1:13" ht="36" customHeight="1">
       <c r="A10" s="19" t="s">
@@ -8560,6 +8750,13 @@
           <t>Fixo + tempo</t>
         </is>
       </c>
+      <c r="N10" s="6"/>
+      <c r="O10" s="21"/>
+      <c r="P10" s="21"/>
+      <c r="Q10" s="21"/>
+      <c r="R10" s="21"/>
+      <c r="S10" s="21"/>
+      <c r="T10" s="21"/>
     </row>
     <row r="11" spans="1:13" ht="36" customHeight="1">
       <c r="A11" s="19" t="s">
@@ -8599,6 +8796,13 @@
           <t>Fixo + tempo</t>
         </is>
       </c>
+      <c r="N11" s="131"/>
+      <c r="O11" s="21"/>
+      <c r="P11" s="21"/>
+      <c r="Q11" s="21"/>
+      <c r="R11" s="21"/>
+      <c r="S11" s="21"/>
+      <c r="T11" s="21"/>
     </row>
     <row r="12" spans="1:13" ht="36" customHeight="1">
       <c r="A12" s="19" t="s">
@@ -8640,6 +8844,13 @@
           <t>Fixo + tempo</t>
         </is>
       </c>
+      <c r="N12" s="6"/>
+      <c r="O12" s="21"/>
+      <c r="P12" s="21"/>
+      <c r="Q12" s="21"/>
+      <c r="R12" s="21"/>
+      <c r="S12" s="21"/>
+      <c r="T12" s="21"/>
     </row>
     <row r="13" spans="1:13" ht="21" customHeight="1">
       <c r="A13" s="19" t="s">
@@ -8681,6 +8892,13 @@
           <t>Fixo + tempo</t>
         </is>
       </c>
+      <c r="N13" s="6"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="21"/>
+      <c r="R13" s="21"/>
+      <c r="S13" s="21"/>
+      <c r="T13" s="21"/>
     </row>
     <row r="14" spans="1:13" ht="21" customHeight="1">
       <c r="A14" s="19" t="s">
@@ -8720,6 +8938,13 @@
           <t>Fixo + tempo</t>
         </is>
       </c>
+      <c r="N14" s="6"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="21"/>
+      <c r="R14" s="21"/>
+      <c r="S14" s="21"/>
+      <c r="T14" s="21"/>
     </row>
     <row r="15" spans="1:13" ht="36" customHeight="1">
       <c r="A15" s="19" t="s">
@@ -8759,6 +8984,13 @@
           <t>Fixo + tempo</t>
         </is>
       </c>
+      <c r="N15" s="131"/>
+      <c r="O15" s="21"/>
+      <c r="P15" s="21"/>
+      <c r="Q15" s="21"/>
+      <c r="R15" s="21"/>
+      <c r="S15" s="21"/>
+      <c r="T15" s="21"/>
     </row>
     <row r="16" spans="1:13" ht="36" customHeight="1">
       <c r="A16" s="19" t="s">
@@ -8800,6 +9032,13 @@
           <t>Fixo + tempo</t>
         </is>
       </c>
+      <c r="N16" s="6"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="21"/>
+      <c r="Q16" s="21"/>
+      <c r="R16" s="21"/>
+      <c r="S16" s="21"/>
+      <c r="T16" s="21"/>
     </row>
     <row r="17" spans="1:13" ht="21" customHeight="1">
       <c r="A17" s="19" t="s">
@@ -8841,6 +9080,13 @@
           <t>Apenas fixo</t>
         </is>
       </c>
+      <c r="N17" s="6"/>
+      <c r="O17" s="21"/>
+      <c r="P17" s="21"/>
+      <c r="Q17" s="21"/>
+      <c r="R17" s="21"/>
+      <c r="S17" s="21"/>
+      <c r="T17" s="21"/>
     </row>
     <row r="18" spans="1:13" ht="21" customHeight="1">
       <c r="A18" s="19" t="s">
@@ -8880,6 +9126,13 @@
           <t>Fixo + tempo</t>
         </is>
       </c>
+      <c r="N18" s="6"/>
+      <c r="O18" s="21"/>
+      <c r="P18" s="21"/>
+      <c r="Q18" s="21"/>
+      <c r="R18" s="21"/>
+      <c r="S18" s="21"/>
+      <c r="T18" s="21"/>
     </row>
     <row r="19" spans="1:13" ht="36" customHeight="1">
       <c r="A19" s="19" t="s">
@@ -8919,6 +9172,13 @@
           <t>Fixo + tempo</t>
         </is>
       </c>
+      <c r="N19" s="131"/>
+      <c r="O19" s="21"/>
+      <c r="P19" s="21"/>
+      <c r="Q19" s="21"/>
+      <c r="R19" s="21"/>
+      <c r="S19" s="21"/>
+      <c r="T19" s="21"/>
     </row>
     <row r="20" spans="1:13" ht="36" customHeight="1">
       <c r="A20" s="19" t="s">
@@ -8960,6 +9220,13 @@
           <t>Fixo + tempo</t>
         </is>
       </c>
+      <c r="N20" s="6"/>
+      <c r="O20" s="21"/>
+      <c r="P20" s="21"/>
+      <c r="Q20" s="21"/>
+      <c r="R20" s="21"/>
+      <c r="S20" s="21"/>
+      <c r="T20" s="21"/>
     </row>
     <row r="21" spans="1:13" ht="36" customHeight="1">
       <c r="A21" s="19" t="s">
@@ -9001,6 +9268,13 @@
           <t>Fixo + tempo</t>
         </is>
       </c>
+      <c r="N21" s="6"/>
+      <c r="O21" s="21"/>
+      <c r="P21" s="21"/>
+      <c r="Q21" s="21"/>
+      <c r="R21" s="21"/>
+      <c r="S21" s="21"/>
+      <c r="T21" s="21"/>
     </row>
     <row r="22" spans="1:13" ht="21" customHeight="1">
       <c r="A22" s="19" t="s">
@@ -9040,6 +9314,13 @@
           <t>Fixo + tempo</t>
         </is>
       </c>
+      <c r="N22" s="6"/>
+      <c r="O22" s="21"/>
+      <c r="P22" s="21"/>
+      <c r="Q22" s="21"/>
+      <c r="R22" s="21"/>
+      <c r="S22" s="21"/>
+      <c r="T22" s="21"/>
     </row>
     <row r="23" spans="1:13" ht="21" customHeight="1">
       <c r="A23" s="19" t="s">
@@ -9079,6 +9360,13 @@
           <t>Fixo + tempo</t>
         </is>
       </c>
+      <c r="N23" s="131"/>
+      <c r="O23" s="21"/>
+      <c r="P23" s="21"/>
+      <c r="Q23" s="21"/>
+      <c r="R23" s="21"/>
+      <c r="S23" s="21"/>
+      <c r="T23" s="21"/>
     </row>
     <row r="24" spans="1:13" ht="36" customHeight="1">
       <c r="A24" s="19" t="s">
@@ -9120,6 +9408,13 @@
           <t>Apenas fixo</t>
         </is>
       </c>
+      <c r="N24" s="6"/>
+      <c r="O24" s="21"/>
+      <c r="P24" s="21"/>
+      <c r="Q24" s="21"/>
+      <c r="R24" s="21"/>
+      <c r="S24" s="21"/>
+      <c r="T24" s="21"/>
     </row>
     <row r="25" spans="1:13" ht="36" customHeight="1">
       <c r="A25" s="19" t="s">
@@ -9161,6 +9456,13 @@
           <t>Apenas fixo</t>
         </is>
       </c>
+      <c r="N25" s="6"/>
+      <c r="O25" s="21"/>
+      <c r="P25" s="21"/>
+      <c r="Q25" s="21"/>
+      <c r="R25" s="21"/>
+      <c r="S25" s="21"/>
+      <c r="T25" s="21"/>
     </row>
     <row r="26" spans="1:13" ht="21" customHeight="1">
       <c r="A26" s="19" t="s">
@@ -9200,6 +9502,13 @@
           <t>Apenas fixo</t>
         </is>
       </c>
+      <c r="N26" s="6"/>
+      <c r="O26" s="21"/>
+      <c r="P26" s="21"/>
+      <c r="Q26" s="21"/>
+      <c r="R26" s="21"/>
+      <c r="S26" s="21"/>
+      <c r="T26" s="21"/>
     </row>
     <row r="27" spans="1:13" ht="21" customHeight="1">
       <c r="A27" s="19" t="s">
@@ -9239,6 +9548,13 @@
           <t>Fixo + tempo</t>
         </is>
       </c>
+      <c r="N27" s="131"/>
+      <c r="O27" s="21"/>
+      <c r="P27" s="21"/>
+      <c r="Q27" s="21"/>
+      <c r="R27" s="21"/>
+      <c r="S27" s="21"/>
+      <c r="T27" s="21"/>
     </row>
     <row r="28" spans="1:13" ht="21" customHeight="1">
       <c r="A28" s="19" t="s">
@@ -9280,6 +9596,13 @@
           <t>Fixo + tempo</t>
         </is>
       </c>
+      <c r="N28" s="6"/>
+      <c r="O28" s="21"/>
+      <c r="P28" s="21"/>
+      <c r="Q28" s="21"/>
+      <c r="R28" s="21"/>
+      <c r="S28" s="21"/>
+      <c r="T28" s="21"/>
     </row>
     <row r="29" spans="1:13" ht="21" customHeight="1">
       <c r="A29" s="19" t="s">
@@ -9321,6 +9644,13 @@
           <t>Fixo + tempo</t>
         </is>
       </c>
+      <c r="N29" s="6"/>
+      <c r="O29" s="21"/>
+      <c r="P29" s="21"/>
+      <c r="Q29" s="21"/>
+      <c r="R29" s="21"/>
+      <c r="S29" s="21"/>
+      <c r="T29" s="21"/>
     </row>
     <row r="30" spans="1:13" ht="36" customHeight="1">
       <c r="A30" s="19" t="s">
@@ -9360,6 +9690,13 @@
           <t>Fixo + tempo</t>
         </is>
       </c>
+      <c r="N30" s="6"/>
+      <c r="O30" s="21"/>
+      <c r="P30" s="21"/>
+      <c r="Q30" s="21"/>
+      <c r="R30" s="21"/>
+      <c r="S30" s="21"/>
+      <c r="T30" s="21"/>
     </row>
     <row r="31" spans="1:13" ht="21" customHeight="1">
       <c r="A31" s="19" t="s">
@@ -9401,6 +9738,13 @@
           <t>Apenas fixo</t>
         </is>
       </c>
+      <c r="N31" s="6"/>
+      <c r="O31" s="21"/>
+      <c r="P31" s="21"/>
+      <c r="Q31" s="21"/>
+      <c r="R31" s="21"/>
+      <c r="S31" s="21"/>
+      <c r="T31" s="21"/>
     </row>
     <row r="32" spans="1:13" ht="21" customHeight="1">
       <c r="A32" s="19" t="s">
@@ -9442,6 +9786,13 @@
           <t>Apenas fixo</t>
         </is>
       </c>
+      <c r="N32" s="6"/>
+      <c r="O32" s="21"/>
+      <c r="P32" s="21"/>
+      <c r="Q32" s="21"/>
+      <c r="R32" s="21"/>
+      <c r="S32" s="21"/>
+      <c r="T32" s="21"/>
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="19"/>
@@ -9457,6 +9808,13 @@
       <c r="K33" s="23"/>
       <c r="L33" s="27"/>
       <c r="M33" s="27"/>
+      <c r="N33" s="6"/>
+      <c r="O33" s="21"/>
+      <c r="P33" s="21"/>
+      <c r="Q33" s="21"/>
+      <c r="R33" s="21"/>
+      <c r="S33" s="21"/>
+      <c r="T33" s="21"/>
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="19"/>
@@ -9472,6 +9830,13 @@
       <c r="K34" s="23"/>
       <c r="L34" s="27"/>
       <c r="M34" s="27"/>
+      <c r="N34" s="6"/>
+      <c r="O34" s="21"/>
+      <c r="P34" s="21"/>
+      <c r="Q34" s="21"/>
+      <c r="R34" s="21"/>
+      <c r="S34" s="21"/>
+      <c r="T34" s="21"/>
     </row>
     <row r="35" spans="1:13" s="1" customFormat="1">
       <c r="A35" s="20"/>
@@ -9487,6 +9852,13 @@
       <c r="K35" s="24"/>
       <c r="L35" s="27"/>
       <c r="M35" s="27"/>
+      <c r="N35" s="18"/>
+      <c r="O35" s="20"/>
+      <c r="P35" s="20"/>
+      <c r="Q35" s="20"/>
+      <c r="R35" s="20"/>
+      <c r="S35" s="20"/>
+      <c r="T35" s="20"/>
     </row>
     <row r="36" spans="1:13" s="1" customFormat="1">
       <c r="A36" s="20"/>
@@ -9502,6 +9874,13 @@
       <c r="K36" s="24"/>
       <c r="L36" s="27"/>
       <c r="M36" s="27"/>
+      <c r="N36" s="18"/>
+      <c r="O36" s="20"/>
+      <c r="P36" s="20"/>
+      <c r="Q36" s="20"/>
+      <c r="R36" s="20"/>
+      <c r="S36" s="20"/>
+      <c r="T36" s="20"/>
     </row>
     <row r="37" spans="1:13" s="1" customFormat="1">
       <c r="A37" s="20"/>
@@ -9517,6 +9896,13 @@
       <c r="K37" s="24"/>
       <c r="L37" s="27"/>
       <c r="M37" s="27"/>
+      <c r="N37" s="18"/>
+      <c r="O37" s="20"/>
+      <c r="P37" s="20"/>
+      <c r="Q37" s="20"/>
+      <c r="R37" s="20"/>
+      <c r="S37" s="20"/>
+      <c r="T37" s="20"/>
     </row>
     <row r="38" spans="1:13" s="1" customFormat="1">
       <c r="A38" s="20"/>
@@ -9532,6 +9918,13 @@
       <c r="K38" s="24"/>
       <c r="L38" s="27"/>
       <c r="M38" s="27"/>
+      <c r="N38" s="18"/>
+      <c r="O38" s="20"/>
+      <c r="P38" s="20"/>
+      <c r="Q38" s="20"/>
+      <c r="R38" s="20"/>
+      <c r="S38" s="20"/>
+      <c r="T38" s="20"/>
     </row>
     <row r="39" spans="1:13" s="1" customFormat="1">
       <c r="A39" s="20"/>
@@ -9547,6 +9940,13 @@
       <c r="K39" s="24"/>
       <c r="L39" s="27"/>
       <c r="M39" s="27"/>
+      <c r="N39" s="18"/>
+      <c r="O39" s="20"/>
+      <c r="P39" s="20"/>
+      <c r="Q39" s="20"/>
+      <c r="R39" s="20"/>
+      <c r="S39" s="20"/>
+      <c r="T39" s="20"/>
     </row>
     <row r="40" spans="1:13" s="1" customFormat="1">
       <c r="A40" s="20"/>
@@ -9562,6 +9962,13 @@
       <c r="K40" s="24"/>
       <c r="L40" s="27"/>
       <c r="M40" s="27"/>
+      <c r="N40" s="18"/>
+      <c r="O40" s="20"/>
+      <c r="P40" s="20"/>
+      <c r="Q40" s="20"/>
+      <c r="R40" s="20"/>
+      <c r="S40" s="20"/>
+      <c r="T40" s="20"/>
     </row>
     <row r="41" spans="1:13" s="1" customFormat="1">
       <c r="A41" s="20"/>
@@ -9577,6 +9984,13 @@
       <c r="K41" s="24"/>
       <c r="L41" s="27"/>
       <c r="M41" s="27"/>
+      <c r="N41" s="18"/>
+      <c r="O41" s="20"/>
+      <c r="P41" s="20"/>
+      <c r="Q41" s="20"/>
+      <c r="R41" s="20"/>
+      <c r="S41" s="20"/>
+      <c r="T41" s="20"/>
     </row>
     <row r="42" spans="1:13" s="1" customFormat="1">
       <c r="A42" s="20"/>
@@ -9592,6 +10006,13 @@
       <c r="K42" s="24"/>
       <c r="L42" s="27"/>
       <c r="M42" s="27"/>
+      <c r="N42" s="18"/>
+      <c r="O42" s="20"/>
+      <c r="P42" s="20"/>
+      <c r="Q42" s="20"/>
+      <c r="R42" s="20"/>
+      <c r="S42" s="20"/>
+      <c r="T42" s="20"/>
     </row>
     <row r="43" spans="1:13" s="1" customFormat="1">
       <c r="A43" s="20"/>
@@ -9607,6 +10028,13 @@
       <c r="K43" s="24"/>
       <c r="L43" s="27"/>
       <c r="M43" s="27"/>
+      <c r="N43" s="18"/>
+      <c r="O43" s="20"/>
+      <c r="P43" s="20"/>
+      <c r="Q43" s="20"/>
+      <c r="R43" s="20"/>
+      <c r="S43" s="20"/>
+      <c r="T43" s="20"/>
     </row>
     <row r="44" spans="1:13" s="1" customFormat="1">
       <c r="A44" s="20"/>
@@ -9622,6 +10050,13 @@
       <c r="K44" s="24"/>
       <c r="L44" s="27"/>
       <c r="M44" s="27"/>
+      <c r="N44" s="18"/>
+      <c r="O44" s="20"/>
+      <c r="P44" s="20"/>
+      <c r="Q44" s="20"/>
+      <c r="R44" s="20"/>
+      <c r="S44" s="20"/>
+      <c r="T44" s="20"/>
     </row>
     <row r="45" spans="1:13" s="1" customFormat="1">
       <c r="A45" s="20"/>
@@ -9637,6 +10072,13 @@
       <c r="K45" s="24"/>
       <c r="L45" s="27"/>
       <c r="M45" s="27"/>
+      <c r="N45" s="18"/>
+      <c r="O45" s="20"/>
+      <c r="P45" s="20"/>
+      <c r="Q45" s="20"/>
+      <c r="R45" s="20"/>
+      <c r="S45" s="20"/>
+      <c r="T45" s="20"/>
     </row>
     <row r="46" spans="1:13" s="1" customFormat="1">
       <c r="A46" s="20"/>
@@ -9652,6 +10094,13 @@
       <c r="K46" s="24"/>
       <c r="L46" s="27"/>
       <c r="M46" s="27"/>
+      <c r="N46" s="18"/>
+      <c r="O46" s="20"/>
+      <c r="P46" s="20"/>
+      <c r="Q46" s="20"/>
+      <c r="R46" s="20"/>
+      <c r="S46" s="20"/>
+      <c r="T46" s="20"/>
     </row>
     <row r="47" spans="1:13" s="1" customFormat="1">
       <c r="A47" s="20"/>
@@ -9667,6 +10116,13 @@
       <c r="K47" s="24"/>
       <c r="L47" s="27"/>
       <c r="M47" s="27"/>
+      <c r="N47" s="18"/>
+      <c r="O47" s="20"/>
+      <c r="P47" s="20"/>
+      <c r="Q47" s="20"/>
+      <c r="R47" s="20"/>
+      <c r="S47" s="20"/>
+      <c r="T47" s="20"/>
     </row>
     <row r="48" spans="1:13" s="1" customFormat="1">
       <c r="A48" s="20"/>
@@ -9682,6 +10138,13 @@
       <c r="K48" s="24"/>
       <c r="L48" s="27"/>
       <c r="M48" s="27"/>
+      <c r="N48" s="18"/>
+      <c r="O48" s="20"/>
+      <c r="P48" s="20"/>
+      <c r="Q48" s="20"/>
+      <c r="R48" s="20"/>
+      <c r="S48" s="20"/>
+      <c r="T48" s="20"/>
     </row>
     <row r="49" spans="1:13" s="1" customFormat="1">
       <c r="A49" s="20"/>
@@ -9697,6 +10160,13 @@
       <c r="K49" s="24"/>
       <c r="L49" s="27"/>
       <c r="M49" s="27"/>
+      <c r="N49" s="18"/>
+      <c r="O49" s="20"/>
+      <c r="P49" s="20"/>
+      <c r="Q49" s="20"/>
+      <c r="R49" s="20"/>
+      <c r="S49" s="20"/>
+      <c r="T49" s="20"/>
     </row>
     <row r="50" spans="1:13" s="1" customFormat="1">
       <c r="A50" s="20"/>
@@ -9712,6 +10182,13 @@
       <c r="K50" s="24"/>
       <c r="L50" s="27"/>
       <c r="M50" s="27"/>
+      <c r="N50" s="18"/>
+      <c r="O50" s="20"/>
+      <c r="P50" s="20"/>
+      <c r="Q50" s="20"/>
+      <c r="R50" s="20"/>
+      <c r="S50" s="20"/>
+      <c r="T50" s="20"/>
     </row>
     <row r="51" spans="1:13" s="1" customFormat="1">
       <c r="A51" s="20"/>
@@ -9727,6 +10204,13 @@
       <c r="K51" s="24"/>
       <c r="L51" s="27"/>
       <c r="M51" s="27"/>
+      <c r="N51" s="18"/>
+      <c r="O51" s="20"/>
+      <c r="P51" s="20"/>
+      <c r="Q51" s="20"/>
+      <c r="R51" s="20"/>
+      <c r="S51" s="20"/>
+      <c r="T51" s="20"/>
     </row>
     <row r="52" spans="1:13" s="1" customFormat="1">
       <c r="A52" s="20"/>
@@ -9742,6 +10226,13 @@
       <c r="K52" s="24"/>
       <c r="L52" s="27"/>
       <c r="M52" s="27"/>
+      <c r="N52" s="18"/>
+      <c r="O52" s="20"/>
+      <c r="P52" s="20"/>
+      <c r="Q52" s="20"/>
+      <c r="R52" s="20"/>
+      <c r="S52" s="20"/>
+      <c r="T52" s="20"/>
     </row>
     <row r="53" spans="1:13" s="1" customFormat="1">
       <c r="A53" s="20"/>
@@ -9757,6 +10248,13 @@
       <c r="K53" s="24"/>
       <c r="L53" s="27"/>
       <c r="M53" s="27"/>
+      <c r="N53" s="18"/>
+      <c r="O53" s="20"/>
+      <c r="P53" s="20"/>
+      <c r="Q53" s="20"/>
+      <c r="R53" s="20"/>
+      <c r="S53" s="20"/>
+      <c r="T53" s="20"/>
     </row>
     <row r="54" spans="1:13" s="1" customFormat="1">
       <c r="A54" s="20"/>
@@ -9772,6 +10270,13 @@
       <c r="K54" s="24"/>
       <c r="L54" s="27"/>
       <c r="M54" s="27"/>
+      <c r="N54" s="18"/>
+      <c r="O54" s="20"/>
+      <c r="P54" s="20"/>
+      <c r="Q54" s="20"/>
+      <c r="R54" s="20"/>
+      <c r="S54" s="20"/>
+      <c r="T54" s="20"/>
     </row>
     <row r="55" spans="1:13" s="1" customFormat="1">
       <c r="A55" s="20"/>
@@ -9787,6 +10292,13 @@
       <c r="K55" s="24"/>
       <c r="L55" s="27"/>
       <c r="M55" s="27"/>
+      <c r="N55" s="18"/>
+      <c r="O55" s="20"/>
+      <c r="P55" s="20"/>
+      <c r="Q55" s="20"/>
+      <c r="R55" s="20"/>
+      <c r="S55" s="20"/>
+      <c r="T55" s="20"/>
     </row>
     <row r="56" spans="1:13" s="1" customFormat="1">
       <c r="A56" s="20"/>
@@ -9802,6 +10314,13 @@
       <c r="K56" s="24"/>
       <c r="L56" s="27"/>
       <c r="M56" s="27"/>
+      <c r="N56" s="18"/>
+      <c r="O56" s="20"/>
+      <c r="P56" s="20"/>
+      <c r="Q56" s="20"/>
+      <c r="R56" s="20"/>
+      <c r="S56" s="20"/>
+      <c r="T56" s="20"/>
     </row>
     <row r="57" spans="1:13" s="1" customFormat="1">
       <c r="A57" s="20"/>
@@ -9817,6 +10336,13 @@
       <c r="K57" s="24"/>
       <c r="L57" s="27"/>
       <c r="M57" s="27"/>
+      <c r="N57" s="18"/>
+      <c r="O57" s="20"/>
+      <c r="P57" s="20"/>
+      <c r="Q57" s="20"/>
+      <c r="R57" s="20"/>
+      <c r="S57" s="20"/>
+      <c r="T57" s="20"/>
     </row>
     <row r="58" spans="1:13" s="1" customFormat="1">
       <c r="A58" s="20"/>
@@ -9832,6 +10358,13 @@
       <c r="K58" s="24"/>
       <c r="L58" s="27"/>
       <c r="M58" s="27"/>
+      <c r="N58" s="18"/>
+      <c r="O58" s="20"/>
+      <c r="P58" s="20"/>
+      <c r="Q58" s="20"/>
+      <c r="R58" s="20"/>
+      <c r="S58" s="20"/>
+      <c r="T58" s="20"/>
     </row>
     <row r="59" spans="1:13" s="1" customFormat="1">
       <c r="A59" s="20"/>
@@ -9847,6 +10380,13 @@
       <c r="K59" s="24"/>
       <c r="L59" s="27"/>
       <c r="M59" s="27"/>
+      <c r="N59" s="18"/>
+      <c r="O59" s="20"/>
+      <c r="P59" s="20"/>
+      <c r="Q59" s="20"/>
+      <c r="R59" s="20"/>
+      <c r="S59" s="20"/>
+      <c r="T59" s="20"/>
     </row>
     <row r="60" spans="1:13" s="1" customFormat="1">
       <c r="A60" s="20"/>
@@ -9862,6 +10402,13 @@
       <c r="K60" s="24"/>
       <c r="L60" s="27"/>
       <c r="M60" s="27"/>
+      <c r="N60" s="18"/>
+      <c r="O60" s="20"/>
+      <c r="P60" s="20"/>
+      <c r="Q60" s="20"/>
+      <c r="R60" s="20"/>
+      <c r="S60" s="20"/>
+      <c r="T60" s="20"/>
     </row>
     <row r="61" spans="1:13" s="1" customFormat="1">
       <c r="A61" s="20"/>
@@ -9877,6 +10424,13 @@
       <c r="K61" s="24"/>
       <c r="L61" s="27"/>
       <c r="M61" s="27"/>
+      <c r="N61" s="18"/>
+      <c r="O61" s="20"/>
+      <c r="P61" s="20"/>
+      <c r="Q61" s="20"/>
+      <c r="R61" s="20"/>
+      <c r="S61" s="20"/>
+      <c r="T61" s="20"/>
     </row>
     <row r="62" spans="1:13" s="1" customFormat="1">
       <c r="A62" s="20"/>
@@ -9892,6 +10446,13 @@
       <c r="K62" s="24"/>
       <c r="L62" s="27"/>
       <c r="M62" s="27"/>
+      <c r="N62" s="18"/>
+      <c r="O62" s="20"/>
+      <c r="P62" s="20"/>
+      <c r="Q62" s="20"/>
+      <c r="R62" s="20"/>
+      <c r="S62" s="20"/>
+      <c r="T62" s="20"/>
     </row>
     <row r="63" spans="1:13" s="1" customFormat="1">
       <c r="A63" s="20"/>
@@ -9907,6 +10468,13 @@
       <c r="K63" s="24"/>
       <c r="L63" s="27"/>
       <c r="M63" s="27"/>
+      <c r="N63" s="18"/>
+      <c r="O63" s="20"/>
+      <c r="P63" s="20"/>
+      <c r="Q63" s="20"/>
+      <c r="R63" s="20"/>
+      <c r="S63" s="20"/>
+      <c r="T63" s="20"/>
     </row>
     <row r="64" spans="1:13" s="1" customFormat="1">
       <c r="A64" s="20"/>
@@ -9922,6 +10490,13 @@
       <c r="K64" s="24"/>
       <c r="L64" s="27"/>
       <c r="M64" s="27"/>
+      <c r="N64" s="18"/>
+      <c r="O64" s="20"/>
+      <c r="P64" s="20"/>
+      <c r="Q64" s="20"/>
+      <c r="R64" s="20"/>
+      <c r="S64" s="20"/>
+      <c r="T64" s="20"/>
     </row>
     <row r="65" spans="1:13" s="1" customFormat="1">
       <c r="A65" s="20"/>
@@ -9937,6 +10512,13 @@
       <c r="K65" s="24"/>
       <c r="L65" s="27"/>
       <c r="M65" s="27"/>
+      <c r="N65" s="18"/>
+      <c r="O65" s="20"/>
+      <c r="P65" s="20"/>
+      <c r="Q65" s="20"/>
+      <c r="R65" s="20"/>
+      <c r="S65" s="20"/>
+      <c r="T65" s="20"/>
     </row>
     <row r="66" spans="1:13" s="1" customFormat="1">
       <c r="A66" s="20"/>
@@ -9952,6 +10534,13 @@
       <c r="K66" s="24"/>
       <c r="L66" s="27"/>
       <c r="M66" s="27"/>
+      <c r="N66" s="18"/>
+      <c r="O66" s="20"/>
+      <c r="P66" s="20"/>
+      <c r="Q66" s="20"/>
+      <c r="R66" s="20"/>
+      <c r="S66" s="20"/>
+      <c r="T66" s="20"/>
     </row>
     <row r="67" spans="1:13" s="1" customFormat="1">
       <c r="A67" s="20"/>
@@ -9967,6 +10556,13 @@
       <c r="K67" s="24"/>
       <c r="L67" s="27"/>
       <c r="M67" s="27"/>
+      <c r="N67" s="18"/>
+      <c r="O67" s="20"/>
+      <c r="P67" s="20"/>
+      <c r="Q67" s="20"/>
+      <c r="R67" s="20"/>
+      <c r="S67" s="20"/>
+      <c r="T67" s="20"/>
     </row>
     <row r="68" spans="1:13" s="1" customFormat="1">
       <c r="A68" s="20"/>
@@ -9982,6 +10578,13 @@
       <c r="K68" s="24"/>
       <c r="L68" s="27"/>
       <c r="M68" s="27"/>
+      <c r="N68" s="18"/>
+      <c r="O68" s="20"/>
+      <c r="P68" s="20"/>
+      <c r="Q68" s="20"/>
+      <c r="R68" s="20"/>
+      <c r="S68" s="20"/>
+      <c r="T68" s="20"/>
     </row>
     <row r="69" spans="1:13" s="1" customFormat="1">
       <c r="A69" s="20"/>
@@ -9997,6 +10600,13 @@
       <c r="K69" s="24"/>
       <c r="L69" s="27"/>
       <c r="M69" s="27"/>
+      <c r="N69" s="18"/>
+      <c r="O69" s="20"/>
+      <c r="P69" s="20"/>
+      <c r="Q69" s="20"/>
+      <c r="R69" s="20"/>
+      <c r="S69" s="20"/>
+      <c r="T69" s="20"/>
     </row>
     <row r="70" spans="1:13" s="1" customFormat="1">
       <c r="A70" s="20"/>
@@ -10012,6 +10622,13 @@
       <c r="K70" s="24"/>
       <c r="L70" s="27"/>
       <c r="M70" s="27"/>
+      <c r="N70" s="18"/>
+      <c r="O70" s="20"/>
+      <c r="P70" s="20"/>
+      <c r="Q70" s="20"/>
+      <c r="R70" s="20"/>
+      <c r="S70" s="20"/>
+      <c r="T70" s="20"/>
     </row>
     <row r="71" spans="1:13" s="1" customFormat="1">
       <c r="A71" s="20"/>
@@ -10027,6 +10644,13 @@
       <c r="K71" s="24"/>
       <c r="L71" s="27"/>
       <c r="M71" s="27"/>
+      <c r="N71" s="18"/>
+      <c r="O71" s="20"/>
+      <c r="P71" s="20"/>
+      <c r="Q71" s="20"/>
+      <c r="R71" s="20"/>
+      <c r="S71" s="20"/>
+      <c r="T71" s="20"/>
     </row>
     <row r="72" spans="1:13" s="1" customFormat="1">
       <c r="A72" s="20"/>
@@ -10042,6 +10666,13 @@
       <c r="K72" s="24"/>
       <c r="L72" s="27"/>
       <c r="M72" s="27"/>
+      <c r="N72" s="18"/>
+      <c r="O72" s="20"/>
+      <c r="P72" s="20"/>
+      <c r="Q72" s="20"/>
+      <c r="R72" s="20"/>
+      <c r="S72" s="20"/>
+      <c r="T72" s="20"/>
     </row>
     <row r="73" spans="1:13" s="1" customFormat="1">
       <c r="A73" s="20"/>
@@ -10057,6 +10688,13 @@
       <c r="K73" s="24"/>
       <c r="L73" s="27"/>
       <c r="M73" s="27"/>
+      <c r="N73" s="18"/>
+      <c r="O73" s="20"/>
+      <c r="P73" s="20"/>
+      <c r="Q73" s="20"/>
+      <c r="R73" s="20"/>
+      <c r="S73" s="20"/>
+      <c r="T73" s="20"/>
     </row>
     <row r="74" spans="1:13" s="1" customFormat="1">
       <c r="A74" s="20"/>
@@ -10072,6 +10710,13 @@
       <c r="K74" s="24"/>
       <c r="L74" s="27"/>
       <c r="M74" s="27"/>
+      <c r="N74" s="18"/>
+      <c r="O74" s="20"/>
+      <c r="P74" s="20"/>
+      <c r="Q74" s="20"/>
+      <c r="R74" s="20"/>
+      <c r="S74" s="20"/>
+      <c r="T74" s="20"/>
     </row>
     <row r="75" spans="1:13" s="1" customFormat="1">
       <c r="A75" s="20"/>
@@ -10087,6 +10732,13 @@
       <c r="K75" s="24"/>
       <c r="L75" s="27"/>
       <c r="M75" s="27"/>
+      <c r="N75" s="18"/>
+      <c r="O75" s="20"/>
+      <c r="P75" s="20"/>
+      <c r="Q75" s="20"/>
+      <c r="R75" s="20"/>
+      <c r="S75" s="20"/>
+      <c r="T75" s="20"/>
     </row>
     <row r="76" spans="1:13" s="1" customFormat="1">
       <c r="A76" s="20"/>
@@ -10102,6 +10754,13 @@
       <c r="K76" s="24"/>
       <c r="L76" s="27"/>
       <c r="M76" s="27"/>
+      <c r="N76" s="18"/>
+      <c r="O76" s="20"/>
+      <c r="P76" s="20"/>
+      <c r="Q76" s="20"/>
+      <c r="R76" s="20"/>
+      <c r="S76" s="20"/>
+      <c r="T76" s="20"/>
     </row>
     <row r="77" spans="1:13" s="1" customFormat="1">
       <c r="A77" s="20"/>
@@ -10117,6 +10776,13 @@
       <c r="K77" s="24"/>
       <c r="L77" s="27"/>
       <c r="M77" s="27"/>
+      <c r="N77" s="18"/>
+      <c r="O77" s="20"/>
+      <c r="P77" s="20"/>
+      <c r="Q77" s="20"/>
+      <c r="R77" s="20"/>
+      <c r="S77" s="20"/>
+      <c r="T77" s="20"/>
     </row>
     <row r="78" spans="1:13" s="1" customFormat="1">
       <c r="A78" s="20"/>
@@ -10132,6 +10798,13 @@
       <c r="K78" s="24"/>
       <c r="L78" s="27"/>
       <c r="M78" s="27"/>
+      <c r="N78" s="18"/>
+      <c r="O78" s="20"/>
+      <c r="P78" s="20"/>
+      <c r="Q78" s="20"/>
+      <c r="R78" s="20"/>
+      <c r="S78" s="20"/>
+      <c r="T78" s="20"/>
     </row>
     <row r="79" spans="1:13" s="1" customFormat="1">
       <c r="A79" s="20"/>
@@ -10147,6 +10820,13 @@
       <c r="K79" s="24"/>
       <c r="L79" s="27"/>
       <c r="M79" s="27"/>
+      <c r="N79" s="18"/>
+      <c r="O79" s="20"/>
+      <c r="P79" s="20"/>
+      <c r="Q79" s="20"/>
+      <c r="R79" s="20"/>
+      <c r="S79" s="20"/>
+      <c r="T79" s="20"/>
     </row>
     <row r="80" spans="1:13" s="1" customFormat="1">
       <c r="A80" s="20"/>
@@ -10162,6 +10842,13 @@
       <c r="K80" s="24"/>
       <c r="L80" s="27"/>
       <c r="M80" s="27"/>
+      <c r="N80" s="18"/>
+      <c r="O80" s="20"/>
+      <c r="P80" s="20"/>
+      <c r="Q80" s="20"/>
+      <c r="R80" s="20"/>
+      <c r="S80" s="20"/>
+      <c r="T80" s="20"/>
     </row>
     <row r="81" spans="1:13" s="1" customFormat="1">
       <c r="A81" s="20"/>
@@ -10177,6 +10864,13 @@
       <c r="K81" s="24"/>
       <c r="L81" s="27"/>
       <c r="M81" s="27"/>
+      <c r="N81" s="18"/>
+      <c r="O81" s="20"/>
+      <c r="P81" s="20"/>
+      <c r="Q81" s="20"/>
+      <c r="R81" s="20"/>
+      <c r="S81" s="20"/>
+      <c r="T81" s="20"/>
     </row>
     <row r="82" spans="1:13" s="1" customFormat="1">
       <c r="A82" s="20"/>
@@ -10192,6 +10886,13 @@
       <c r="K82" s="24"/>
       <c r="L82" s="27"/>
       <c r="M82" s="27"/>
+      <c r="N82" s="18"/>
+      <c r="O82" s="20"/>
+      <c r="P82" s="20"/>
+      <c r="Q82" s="20"/>
+      <c r="R82" s="20"/>
+      <c r="S82" s="20"/>
+      <c r="T82" s="20"/>
     </row>
     <row r="83" spans="1:13" s="1" customFormat="1">
       <c r="A83" s="20"/>
@@ -10207,6 +10908,13 @@
       <c r="K83" s="24"/>
       <c r="L83" s="27"/>
       <c r="M83" s="27"/>
+      <c r="N83" s="18"/>
+      <c r="O83" s="20"/>
+      <c r="P83" s="20"/>
+      <c r="Q83" s="20"/>
+      <c r="R83" s="20"/>
+      <c r="S83" s="20"/>
+      <c r="T83" s="20"/>
     </row>
     <row r="84" spans="1:13" s="1" customFormat="1">
       <c r="A84" s="20"/>
@@ -10222,6 +10930,13 @@
       <c r="K84" s="24"/>
       <c r="L84" s="27"/>
       <c r="M84" s="27"/>
+      <c r="N84" s="18"/>
+      <c r="O84" s="20"/>
+      <c r="P84" s="20"/>
+      <c r="Q84" s="20"/>
+      <c r="R84" s="20"/>
+      <c r="S84" s="20"/>
+      <c r="T84" s="20"/>
     </row>
     <row r="85" spans="1:13" s="1" customFormat="1">
       <c r="A85" s="20"/>
@@ -10237,6 +10952,13 @@
       <c r="K85" s="24"/>
       <c r="L85" s="27"/>
       <c r="M85" s="27"/>
+      <c r="N85" s="18"/>
+      <c r="O85" s="20"/>
+      <c r="P85" s="20"/>
+      <c r="Q85" s="20"/>
+      <c r="R85" s="20"/>
+      <c r="S85" s="20"/>
+      <c r="T85" s="20"/>
     </row>
     <row r="86" spans="1:13" s="1" customFormat="1">
       <c r="A86" s="20"/>
@@ -10252,6 +10974,13 @@
       <c r="K86" s="24"/>
       <c r="L86" s="27"/>
       <c r="M86" s="27"/>
+      <c r="N86" s="18"/>
+      <c r="O86" s="20"/>
+      <c r="P86" s="20"/>
+      <c r="Q86" s="20"/>
+      <c r="R86" s="20"/>
+      <c r="S86" s="20"/>
+      <c r="T86" s="20"/>
     </row>
     <row r="87" spans="1:13" s="1" customFormat="1">
       <c r="A87" s="20"/>
@@ -10267,6 +10996,13 @@
       <c r="K87" s="24"/>
       <c r="L87" s="27"/>
       <c r="M87" s="27"/>
+      <c r="N87" s="18"/>
+      <c r="O87" s="20"/>
+      <c r="P87" s="20"/>
+      <c r="Q87" s="20"/>
+      <c r="R87" s="20"/>
+      <c r="S87" s="20"/>
+      <c r="T87" s="20"/>
     </row>
     <row r="88" spans="1:13" s="1" customFormat="1">
       <c r="A88" s="20"/>
@@ -10282,6 +11018,13 @@
       <c r="K88" s="24"/>
       <c r="L88" s="27"/>
       <c r="M88" s="27"/>
+      <c r="N88" s="18"/>
+      <c r="O88" s="20"/>
+      <c r="P88" s="20"/>
+      <c r="Q88" s="20"/>
+      <c r="R88" s="20"/>
+      <c r="S88" s="20"/>
+      <c r="T88" s="20"/>
     </row>
     <row r="89" spans="1:13" s="1" customFormat="1">
       <c r="A89" s="20"/>
@@ -10297,6 +11040,13 @@
       <c r="K89" s="24"/>
       <c r="L89" s="27"/>
       <c r="M89" s="27"/>
+      <c r="N89" s="18"/>
+      <c r="O89" s="20"/>
+      <c r="P89" s="20"/>
+      <c r="Q89" s="20"/>
+      <c r="R89" s="20"/>
+      <c r="S89" s="20"/>
+      <c r="T89" s="20"/>
     </row>
     <row r="90" spans="1:13" s="1" customFormat="1">
       <c r="A90" s="20"/>
@@ -10312,6 +11062,13 @@
       <c r="K90" s="24"/>
       <c r="L90" s="27"/>
       <c r="M90" s="27"/>
+      <c r="N90" s="18"/>
+      <c r="O90" s="20"/>
+      <c r="P90" s="20"/>
+      <c r="Q90" s="20"/>
+      <c r="R90" s="20"/>
+      <c r="S90" s="20"/>
+      <c r="T90" s="20"/>
     </row>
     <row r="91" spans="1:13" s="1" customFormat="1">
       <c r="A91" s="20"/>
@@ -10327,6 +11084,13 @@
       <c r="K91" s="24"/>
       <c r="L91" s="27"/>
       <c r="M91" s="27"/>
+      <c r="N91" s="18"/>
+      <c r="O91" s="20"/>
+      <c r="P91" s="20"/>
+      <c r="Q91" s="20"/>
+      <c r="R91" s="20"/>
+      <c r="S91" s="20"/>
+      <c r="T91" s="20"/>
     </row>
     <row r="92" spans="1:13" s="1" customFormat="1">
       <c r="A92" s="20"/>
@@ -10342,6 +11106,13 @@
       <c r="K92" s="24"/>
       <c r="L92" s="27"/>
       <c r="M92" s="27"/>
+      <c r="N92" s="18"/>
+      <c r="O92" s="20"/>
+      <c r="P92" s="20"/>
+      <c r="Q92" s="20"/>
+      <c r="R92" s="20"/>
+      <c r="S92" s="20"/>
+      <c r="T92" s="20"/>
     </row>
     <row r="93" spans="1:13" s="1" customFormat="1">
       <c r="A93" s="20"/>
@@ -10357,6 +11128,13 @@
       <c r="K93" s="24"/>
       <c r="L93" s="27"/>
       <c r="M93" s="27"/>
+      <c r="N93" s="18"/>
+      <c r="O93" s="20"/>
+      <c r="P93" s="20"/>
+      <c r="Q93" s="20"/>
+      <c r="R93" s="20"/>
+      <c r="S93" s="20"/>
+      <c r="T93" s="20"/>
     </row>
     <row r="94" spans="1:13" s="1" customFormat="1">
       <c r="A94" s="20"/>
@@ -10372,6 +11150,13 @@
       <c r="K94" s="24"/>
       <c r="L94" s="27"/>
       <c r="M94" s="27"/>
+      <c r="N94" s="18"/>
+      <c r="O94" s="20"/>
+      <c r="P94" s="20"/>
+      <c r="Q94" s="20"/>
+      <c r="R94" s="20"/>
+      <c r="S94" s="20"/>
+      <c r="T94" s="20"/>
     </row>
     <row r="95" spans="1:13" s="1" customFormat="1">
       <c r="A95" s="20"/>
@@ -10387,6 +11172,13 @@
       <c r="K95" s="24"/>
       <c r="L95" s="27"/>
       <c r="M95" s="27"/>
+      <c r="N95" s="18"/>
+      <c r="O95" s="20"/>
+      <c r="P95" s="20"/>
+      <c r="Q95" s="20"/>
+      <c r="R95" s="20"/>
+      <c r="S95" s="20"/>
+      <c r="T95" s="20"/>
     </row>
     <row r="96" spans="1:13" s="1" customFormat="1">
       <c r="A96" s="20"/>
@@ -10402,6 +11194,13 @@
       <c r="K96" s="24"/>
       <c r="L96" s="27"/>
       <c r="M96" s="27"/>
+      <c r="N96" s="18"/>
+      <c r="O96" s="20"/>
+      <c r="P96" s="20"/>
+      <c r="Q96" s="20"/>
+      <c r="R96" s="20"/>
+      <c r="S96" s="20"/>
+      <c r="T96" s="20"/>
     </row>
     <row r="97" spans="1:13" s="1" customFormat="1">
       <c r="A97" s="20"/>
@@ -10417,6 +11216,13 @@
       <c r="K97" s="24"/>
       <c r="L97" s="27"/>
       <c r="M97" s="27"/>
+      <c r="N97" s="18"/>
+      <c r="O97" s="20"/>
+      <c r="P97" s="20"/>
+      <c r="Q97" s="20"/>
+      <c r="R97" s="20"/>
+      <c r="S97" s="20"/>
+      <c r="T97" s="20"/>
     </row>
     <row r="98" spans="1:13" s="1" customFormat="1">
       <c r="A98" s="20"/>
@@ -10432,6 +11238,13 @@
       <c r="K98" s="24"/>
       <c r="L98" s="27"/>
       <c r="M98" s="27"/>
+      <c r="N98" s="18"/>
+      <c r="O98" s="20"/>
+      <c r="P98" s="20"/>
+      <c r="Q98" s="20"/>
+      <c r="R98" s="20"/>
+      <c r="S98" s="20"/>
+      <c r="T98" s="20"/>
     </row>
     <row r="99" spans="1:13" s="1" customFormat="1">
       <c r="A99" s="20"/>
@@ -10447,29 +11260,81 @@
       <c r="K99" s="24"/>
       <c r="L99" s="27"/>
       <c r="M99" s="27"/>
+      <c r="N99" s="18"/>
+      <c r="O99" s="20"/>
+      <c r="P99" s="20"/>
+      <c r="Q99" s="20"/>
+      <c r="R99" s="20"/>
+      <c r="S99" s="20"/>
+      <c r="T99" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="E3:E99">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="8" priority="10">
       <formula>$D3="Fixa"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:H99">
-    <cfRule type="expression" dxfId="7" priority="2">
+  <conditionalFormatting sqref="F3:F99">
+    <cfRule type="expression" dxfId="7" priority="11">
+      <formula>OR($D3="Triangular",$D3="Beta-PERT",$D3="Uniforme")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3:G99">
+    <cfRule type="expression" dxfId="7" priority="12">
       <formula>OR($D3="Triangular",$D3="Beta-PERT")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:J99">
-    <cfRule type="expression" dxfId="6" priority="3">
-      <formula>$D3="Normal"</formula>
+  <conditionalFormatting sqref="H3:H99">
+    <cfRule type="expression" dxfId="7" priority="13">
+      <formula>OR($D3="Triangular",$D3="Beta-PERT",$D3="Uniforme")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
+  <conditionalFormatting sqref="I3:I99">
+    <cfRule type="expression" dxfId="6" priority="14">
+      <formula>OR($D3="Normal",$D3="Exponencial",$D3="Lognormal",$D3="Gama")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J3:J99">
+    <cfRule type="expression" dxfId="6" priority="15">
+      <formula>OR($D3="Normal",$D3="Lognormal",$D3="Gama")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O3:O99">
+    <cfRule type="expression" dxfId="8" priority="16">
+      <formula>$N3="Fixa"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P3:P99">
+    <cfRule type="expression" dxfId="7" priority="17">
+      <formula>OR($N3="Triangular",$N3="Beta-PERT",$N3="Uniforme")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q3:Q99">
+    <cfRule type="expression" dxfId="7" priority="18">
+      <formula>OR($N3="Triangular",$N3="Beta-PERT")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R3:R99">
+    <cfRule type="expression" dxfId="7" priority="19">
+      <formula>OR($N3="Triangular",$N3="Beta-PERT",$N3="Uniforme")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S3:S99">
+    <cfRule type="expression" dxfId="6" priority="20">
+      <formula>OR($N3="Normal",$N3="Exponencial",$N3="Lognormal",$N3="Gama")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T3:T99">
+    <cfRule type="expression" dxfId="6" priority="21">
+      <formula>OR($N3="Normal",$N3="Lognormal",$N3="Gama")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="4">
     <dataValidation type="list" sqref="D3:D99" xr:uid="{00000000-0002-0000-0200-000000000000}">
-      <formula1>"Fixa,Triangular,Beta-PERT,Normal"</formula1>
+      <formula1>"Fixa,Triangular,Beta-PERT,Uniforme,Normal,Exponencial,Lognormal,Gama"</formula1>
     </dataValidation>
     <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" errorTitle="Invalid input" error="Enter a value from the documented options or range." sqref="K3:L99" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>0</formula1>
@@ -10477,6 +11342,9 @@
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" error="Choose Fixed only or Fixed + time." sqref="M3:M99" xr:uid="{00000000-0002-0000-0200-000002000000}">
       <formula1>"Apenas fixo,Fixo + tempo"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="N3:N99">
+      <formula1>"Fixa,Triangular,Beta-PERT,Uniforme,Normal,Exponencial,Lognormal,Gama"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15465,7 +16333,7 @@
       <formula1>"Aberto,Em monitoramento,Encerrado"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="N3:N99" xr:uid="{00000000-0002-0000-0300-000006000000}">
-      <formula1>"Fixa,Triangular,Beta-PERT,Normal"</formula1>
+      <formula1>"Fixa,Triangular,Beta-PERT,Uniforme,Normal,Exponencial,Lognormal,Gama"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="P3:P99" xr:uid="{00000000-0002-0000-0300-000007000000}">
       <formula1>"verdadeiro,falso"</formula1>
@@ -22492,28 +23360,33 @@
     <mergeCell ref="A1:J1"/>
   </mergeCells>
   <conditionalFormatting sqref="E3:E299">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="5" priority="22">
       <formula>$D3="Fixa"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F299">
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="4" priority="23">
       <formula>OR($D3="Triangular",$D3="Beta-PERT",$D3="Uniforme")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G299">
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="3" priority="24">
       <formula>OR($D3="Triangular",$D3="Beta-PERT")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H299">
-    <cfRule type="expression" dxfId="2" priority="4">
+    <cfRule type="expression" dxfId="2" priority="25">
       <formula>OR($D3="Triangular",$D3="Beta-PERT",$D3="Uniforme")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:J299">
-    <cfRule type="expression" dxfId="1" priority="5">
-      <formula>$D3="Normal"</formula>
+  <conditionalFormatting sqref="I3:I299">
+    <cfRule type="expression" dxfId="1" priority="26">
+      <formula>OR($D3="Normal",$D3="Exponencial",$D3="Lognormal",$D3="Gama")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J3:J299">
+    <cfRule type="expression" dxfId="1" priority="27">
+      <formula>OR($D3="Normal",$D3="Lognormal",$D3="Gama")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
@@ -22521,7 +23394,7 @@
       <formula1>"Duração,Custo"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid input" error="Enter a value from the documented options or range." sqref="D3:D299" xr:uid="{00000000-0002-0000-0400-000001000000}">
-      <formula1>"Fixa,Triangular,Beta-PERT,Uniforme,Normal"</formula1>
+      <formula1>"Fixa,Triangular,Beta-PERT,Uniforme,Normal,Exponencial,Lognormal,Gama"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
